--- a/tools/excel/ENS_decreto/ENS-RD-311-2022.xlsx
+++ b/tools/excel/ENS_decreto/ENS-RD-311-2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\ENS_decreto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C00E6D9-6569-42BE-831A-F6012E4DA0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8609FDDE-7B6E-432E-963D-D898EE835BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="2975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4715" uniqueCount="2975">
   <si>
     <t>type</t>
   </si>
@@ -7110,9 +7110,6 @@
     <t>Acquisition of new components</t>
   </si>
   <si>
-    <t>Implementation of the measur</t>
-  </si>
-  <si>
     <t>Dimensions : All
 – BASIC category: op.pl.3.
 – MEDIUM category: op.pl.3.
@@ -9464,6 +9461,12 @@
   </si>
   <si>
     <t>imp_grp</t>
+  </si>
+  <si>
+    <t>Dimensions : All
+– BASIC Category: mp.si.4.
+– MEDIUM Category: mp.si.4.
+– HIGH Category: mp.si.4.</t>
   </si>
 </sst>
 </file>
@@ -9657,7 +9660,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -9867,40 +9870,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{DA831D20-FBF9-46BB-A6BC-D7A7E3BDEB13}"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -9966,6 +9947,34 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -10056,14 +10065,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BA5E398C-A2C7-41D5-A278-68D796827DB8}" name="Tableau2" displayName="Tableau2" ref="A1:E12" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BA5E398C-A2C7-41D5-A278-68D796827DB8}" name="Tableau2" displayName="Tableau2" ref="A1:E12" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E12" xr:uid="{BA5E398C-A2C7-41D5-A278-68D796827DB8}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{67421716-27DB-41EA-9D10-2396CC121D8D}" name="ref_id" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{53276570-5536-4038-B764-421247D40F8D}" name="name" dataDxfId="5" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{ECD63ED6-9182-4967-AD7D-3887ACAA19C2}" name="description" dataDxfId="4" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{0F977F10-409B-448D-AFAE-D1F7A41DC6D5}" name="name[en]" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{C63F524E-6A81-40F3-AE58-86FD8321F4FE}" name="description[en]" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{67421716-27DB-41EA-9D10-2396CC121D8D}" name="ref_id" dataDxfId="4" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{53276570-5536-4038-B764-421247D40F8D}" name="name" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{ECD63ED6-9182-4967-AD7D-3887ACAA19C2}" name="description" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{0F977F10-409B-448D-AFAE-D1F7A41DC6D5}" name="name[en]" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{C63F524E-6A81-40F3-AE58-86FD8321F4FE}" name="description[en]" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10382,7 +10391,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -10443,10 +10452,10 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="61" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
@@ -10454,7 +10463,7 @@
         <v>1914</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
     </row>
   </sheetData>
@@ -10524,15 +10533,15 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
@@ -10540,7 +10549,7 @@
         <v>1914</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
     </row>
   </sheetData>
@@ -10570,7 +10579,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="67" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="C1" s="67" t="s">
         <v>7</v>
@@ -10585,10 +10594,10 @@
         <v>24</v>
       </c>
       <c r="G1" s="69" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H1" s="73" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="I1" s="74" t="s">
         <v>1914</v>
@@ -16738,10 +16747,10 @@
       <c r="E314" s="27"/>
       <c r="F314" s="2"/>
       <c r="G314" s="27"/>
-      <c r="H314" s="48"/>
-      <c r="I314" s="1" t="s">
+      <c r="H314" s="1" t="s">
         <v>2204</v>
       </c>
+      <c r="I314" s="83"/>
     </row>
     <row r="315" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A315" s="10" t="s">
@@ -17088,10 +17097,10 @@
       <c r="E330" s="27"/>
       <c r="F330" s="2"/>
       <c r="G330" s="28"/>
-      <c r="H330" s="48"/>
-      <c r="I330" s="1" t="s">
+      <c r="H330" s="1" t="s">
         <v>2219</v>
       </c>
+      <c r="I330" s="83"/>
     </row>
     <row r="331" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A331" s="10" t="s">
@@ -17412,7 +17421,7 @@
       </c>
       <c r="G345" s="24"/>
       <c r="H345" s="57" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>656</v>
@@ -17623,10 +17632,10 @@
       <c r="E355" s="27"/>
       <c r="F355" s="2"/>
       <c r="G355" s="29"/>
-      <c r="H355" s="48"/>
-      <c r="I355" s="1" t="s">
+      <c r="H355" s="1" t="s">
         <v>2240</v>
       </c>
+      <c r="I355" s="83"/>
     </row>
     <row r="356" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A356" s="10"/>
@@ -17749,10 +17758,10 @@
       <c r="E361" s="27"/>
       <c r="F361" s="2"/>
       <c r="G361" s="29"/>
-      <c r="H361" s="48"/>
-      <c r="I361" s="1" t="s">
+      <c r="H361" s="1" t="s">
         <v>2246</v>
       </c>
+      <c r="I361" s="83"/>
     </row>
     <row r="362" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A362" s="10"/>
@@ -17903,7 +17912,7 @@
       <c r="F368" s="2"/>
       <c r="G368" s="28"/>
       <c r="H368" s="53" t="s">
-        <v>2252</v>
+        <v>2192</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>656</v>
@@ -18049,10 +18058,10 @@
       <c r="E375" s="27"/>
       <c r="F375" s="2"/>
       <c r="G375" s="29"/>
-      <c r="H375" s="48"/>
-      <c r="I375" s="1" t="s">
+      <c r="H375" s="1" t="s">
         <v>2259</v>
       </c>
+      <c r="I375" s="83"/>
     </row>
     <row r="376" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A376" s="10" t="s">
@@ -18089,10 +18098,10 @@
       <c r="E377" s="27"/>
       <c r="F377" s="2"/>
       <c r="G377" s="29"/>
-      <c r="H377" s="48"/>
-      <c r="I377" s="1" t="s">
+      <c r="H377" s="1" t="s">
         <v>2261</v>
       </c>
+      <c r="I377" s="83"/>
     </row>
     <row r="378" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A378" s="10" t="s">
@@ -18129,10 +18138,10 @@
       <c r="E379" s="27"/>
       <c r="F379" s="2"/>
       <c r="G379" s="29"/>
-      <c r="H379" s="48"/>
-      <c r="I379" s="1" t="s">
+      <c r="H379" s="1" t="s">
         <v>2263</v>
       </c>
+      <c r="I379" s="83"/>
     </row>
     <row r="380" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A380" s="10" t="s">
@@ -18195,7 +18204,7 @@
       <c r="F382" s="2"/>
       <c r="G382" s="28"/>
       <c r="H382" s="53" t="s">
-        <v>2266</v>
+        <v>2192</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>656</v>
@@ -18215,7 +18224,7 @@
       <c r="G383" s="28"/>
       <c r="H383" s="48"/>
       <c r="I383" s="58" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="384" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -18234,7 +18243,7 @@
       <c r="G384" s="2"/>
       <c r="H384" s="48"/>
       <c r="I384" s="1" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="385" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18257,7 +18266,7 @@
       <c r="G385" s="29"/>
       <c r="H385" s="48"/>
       <c r="I385" s="1" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="386" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18280,7 +18289,7 @@
       <c r="G386" s="29"/>
       <c r="H386" s="48"/>
       <c r="I386" s="1" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="387" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -18303,7 +18312,7 @@
       <c r="G387" s="29"/>
       <c r="H387" s="48"/>
       <c r="I387" s="1" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="388" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18325,7 +18334,7 @@
       </c>
       <c r="G388" s="8"/>
       <c r="H388" s="53" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>656</v>
@@ -18364,7 +18373,7 @@
       <c r="G390" s="28"/>
       <c r="H390" s="53"/>
       <c r="I390" s="48" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="391" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -18383,7 +18392,7 @@
       <c r="G391" s="2"/>
       <c r="H391" s="48"/>
       <c r="I391" s="1" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="392" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18406,7 +18415,7 @@
       <c r="G392" s="29"/>
       <c r="H392" s="48"/>
       <c r="I392" s="1" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="393" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -18429,7 +18438,7 @@
       <c r="G393" s="29"/>
       <c r="H393" s="48"/>
       <c r="I393" s="1" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="394" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18452,7 +18461,7 @@
       <c r="G394" s="29"/>
       <c r="H394" s="48"/>
       <c r="I394" s="1" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="395" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18475,7 +18484,7 @@
       <c r="G395" s="29"/>
       <c r="H395" s="48"/>
       <c r="I395" s="1" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="396" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18498,7 +18507,7 @@
       <c r="G396" s="29"/>
       <c r="H396" s="48"/>
       <c r="I396" s="1" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="397" spans="1:9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -18514,7 +18523,7 @@
       <c r="F397" s="2"/>
       <c r="G397" s="29"/>
       <c r="H397" s="48" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>656</v>
@@ -18540,7 +18549,7 @@
       <c r="G398" s="29"/>
       <c r="H398" s="48"/>
       <c r="I398" s="1" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="399" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18563,7 +18572,7 @@
       <c r="G399" s="29"/>
       <c r="H399" s="48"/>
       <c r="I399" s="1" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="400" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18585,7 +18594,7 @@
       </c>
       <c r="G400" s="8"/>
       <c r="H400" s="53" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>656</v>
@@ -18604,7 +18613,7 @@
       <c r="F401" s="2"/>
       <c r="G401" s="28"/>
       <c r="H401" s="48" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>656</v>
@@ -18624,7 +18633,7 @@
       <c r="G402" s="28"/>
       <c r="H402" s="48"/>
       <c r="I402" s="58" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="403" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -18647,7 +18656,7 @@
       <c r="G403" s="29"/>
       <c r="H403" s="48"/>
       <c r="I403" s="1" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="404" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -18666,7 +18675,7 @@
       <c r="G404" s="29"/>
       <c r="H404" s="48"/>
       <c r="I404" s="1" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="405" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -18685,7 +18694,7 @@
       <c r="G405" s="29"/>
       <c r="H405" s="48"/>
       <c r="I405" s="1" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="406" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -18708,7 +18717,7 @@
       <c r="G406" s="29"/>
       <c r="H406" s="48"/>
       <c r="I406" s="1" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="407" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18724,7 +18733,7 @@
       <c r="F407" s="2"/>
       <c r="G407" s="29"/>
       <c r="H407" s="48" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>656</v>
@@ -18750,7 +18759,7 @@
       <c r="G408" s="29"/>
       <c r="H408" s="48"/>
       <c r="I408" s="1" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="409" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18766,7 +18775,7 @@
       <c r="F409" s="2"/>
       <c r="G409" s="29"/>
       <c r="H409" s="48" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>656</v>
@@ -18792,7 +18801,7 @@
       <c r="G410" s="29"/>
       <c r="H410" s="48"/>
       <c r="I410" s="1" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="411" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18814,7 +18823,7 @@
       </c>
       <c r="G411" s="19"/>
       <c r="H411" s="56" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>656</v>
@@ -18836,7 +18845,7 @@
       <c r="G412" s="2"/>
       <c r="H412" s="48"/>
       <c r="I412" s="1" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="413" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -18855,7 +18864,7 @@
       <c r="G413" s="2"/>
       <c r="H413" s="48"/>
       <c r="I413" s="1" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="414" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -18874,7 +18883,7 @@
       <c r="G414" s="2"/>
       <c r="H414" s="48"/>
       <c r="I414" s="1" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="415" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -18896,7 +18905,7 @@
       </c>
       <c r="G415" s="8"/>
       <c r="H415" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="I415" s="66" t="s">
         <v>656</v>
@@ -18915,7 +18924,7 @@
       <c r="F416" s="2"/>
       <c r="G416" s="28"/>
       <c r="H416" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>656</v>
@@ -18935,7 +18944,7 @@
       <c r="G417" s="28"/>
       <c r="H417" s="48"/>
       <c r="I417" s="58" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="418" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -18954,7 +18963,7 @@
       <c r="G418" s="2"/>
       <c r="H418" s="48"/>
       <c r="I418" s="1" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="419" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -18977,7 +18986,7 @@
       <c r="G419" s="29"/>
       <c r="H419" s="48"/>
       <c r="I419" s="1" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="420" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -19000,7 +19009,7 @@
       <c r="G420" s="29"/>
       <c r="H420" s="48"/>
       <c r="I420" s="1" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="421" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -19023,7 +19032,7 @@
       <c r="G421" s="29"/>
       <c r="H421" s="48"/>
       <c r="I421" s="1" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="422" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19044,7 +19053,7 @@
       <c r="G422" s="29"/>
       <c r="H422" s="48"/>
       <c r="I422" s="1" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="423" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19067,7 +19076,7 @@
       <c r="G423" s="29"/>
       <c r="H423" s="48"/>
       <c r="I423" s="1" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="424" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -19090,7 +19099,7 @@
       <c r="G424" s="29"/>
       <c r="H424" s="48"/>
       <c r="I424" s="1" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="425" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -19113,7 +19122,7 @@
       <c r="G425" s="29"/>
       <c r="H425" s="48"/>
       <c r="I425" s="1" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="426" spans="1:9" customFormat="1" ht="156" x14ac:dyDescent="0.3">
@@ -19134,7 +19143,7 @@
       <c r="G426" s="29"/>
       <c r="H426" s="48"/>
       <c r="I426" s="1" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="427" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19157,7 +19166,7 @@
       <c r="G427" s="29"/>
       <c r="H427" s="48"/>
       <c r="I427" s="1" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="428" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19180,7 +19189,7 @@
       <c r="G428" s="29"/>
       <c r="H428" s="48"/>
       <c r="I428" s="1" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="429" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19203,7 +19212,7 @@
       <c r="G429" s="29"/>
       <c r="H429" s="48"/>
       <c r="I429" s="1" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="430" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19219,7 +19228,7 @@
       <c r="F430" s="2"/>
       <c r="G430" s="29"/>
       <c r="H430" s="48" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="I430" s="1" t="s">
         <v>656</v>
@@ -19245,7 +19254,7 @@
       <c r="G431" s="29"/>
       <c r="H431" s="48"/>
       <c r="I431" s="1" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="432" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -19268,7 +19277,7 @@
       <c r="G432" s="29"/>
       <c r="H432" s="48"/>
       <c r="I432" s="1" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="433" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19291,7 +19300,7 @@
       <c r="G433" s="29"/>
       <c r="H433" s="48"/>
       <c r="I433" s="1" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="434" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19313,7 +19322,7 @@
       </c>
       <c r="G434" s="8"/>
       <c r="H434" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>656</v>
@@ -19332,7 +19341,7 @@
       <c r="F435" s="2"/>
       <c r="G435" s="28"/>
       <c r="H435" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>656</v>
@@ -19352,7 +19361,7 @@
       <c r="G436" s="28"/>
       <c r="H436" s="48"/>
       <c r="I436" s="58" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="437" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19375,7 +19384,7 @@
       <c r="G437" s="29"/>
       <c r="H437" s="48"/>
       <c r="I437" s="1" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="438" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -19398,7 +19407,7 @@
       <c r="G438" s="29"/>
       <c r="H438" s="48"/>
       <c r="I438" s="1" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="439" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19421,7 +19430,7 @@
       <c r="G439" s="29"/>
       <c r="H439" s="48"/>
       <c r="I439" s="1" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="440" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19437,7 +19446,7 @@
       <c r="F440" s="2"/>
       <c r="G440" s="29"/>
       <c r="H440" s="48" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="I440" s="1" t="s">
         <v>656</v>
@@ -19463,7 +19472,7 @@
       <c r="G441" s="29"/>
       <c r="H441" s="48"/>
       <c r="I441" s="1" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="442" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19486,7 +19495,7 @@
       <c r="G442" s="29"/>
       <c r="H442" s="48"/>
       <c r="I442" s="1" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="443" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19502,7 +19511,7 @@
       <c r="F443" s="2"/>
       <c r="G443" s="29"/>
       <c r="H443" s="48" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>656</v>
@@ -19528,7 +19537,7 @@
       <c r="G444" s="29"/>
       <c r="H444" s="48"/>
       <c r="I444" s="1" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="445" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19550,7 +19559,7 @@
       </c>
       <c r="G445" s="8"/>
       <c r="H445" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="I445" s="1" t="s">
         <v>656</v>
@@ -19569,7 +19578,7 @@
       <c r="F446" s="2"/>
       <c r="G446" s="28"/>
       <c r="H446" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I446" s="1" t="s">
         <v>656</v>
@@ -19589,7 +19598,7 @@
       <c r="G447" s="28"/>
       <c r="H447" s="53"/>
       <c r="I447" s="58" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="448" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -19608,7 +19617,7 @@
       <c r="G448" s="29"/>
       <c r="H448" s="48"/>
       <c r="I448" s="1" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="449" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19631,7 +19640,7 @@
       <c r="G449" s="29"/>
       <c r="H449" s="48"/>
       <c r="I449" s="1" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="450" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19654,7 +19663,7 @@
       <c r="G450" s="29"/>
       <c r="H450" s="48"/>
       <c r="I450" s="1" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="451" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19670,7 +19679,7 @@
       <c r="F451" s="2"/>
       <c r="G451" s="29"/>
       <c r="H451" s="48" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>656</v>
@@ -19696,7 +19705,7 @@
       <c r="G452" s="29"/>
       <c r="H452" s="48"/>
       <c r="I452" s="1" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="453" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19719,7 +19728,7 @@
       <c r="G453" s="29"/>
       <c r="H453" s="48"/>
       <c r="I453" s="1" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="454" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19735,7 +19744,7 @@
       <c r="F454" s="2"/>
       <c r="G454" s="29"/>
       <c r="H454" s="48" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>656</v>
@@ -19761,7 +19770,7 @@
       <c r="G455" s="29"/>
       <c r="H455" s="48"/>
       <c r="I455" s="1" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="456" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19777,7 +19786,7 @@
       <c r="F456" s="2"/>
       <c r="G456" s="29"/>
       <c r="H456" s="48" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>656</v>
@@ -19803,7 +19812,7 @@
       <c r="G457" s="29"/>
       <c r="H457" s="48"/>
       <c r="I457" s="1" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="458" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19825,7 +19834,7 @@
       </c>
       <c r="G458" s="8"/>
       <c r="H458" s="48" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>656</v>
@@ -19844,7 +19853,7 @@
       <c r="F459" s="2"/>
       <c r="G459" s="28"/>
       <c r="H459" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>656</v>
@@ -19864,7 +19873,7 @@
       <c r="G460" s="28"/>
       <c r="H460" s="48"/>
       <c r="I460" s="58" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="461" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19883,7 +19892,7 @@
       <c r="G461" s="2"/>
       <c r="H461" s="48"/>
       <c r="I461" s="1" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="462" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -19906,7 +19915,7 @@
       <c r="G462" s="29"/>
       <c r="H462" s="48"/>
       <c r="I462" s="1" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="463" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19929,7 +19938,7 @@
       <c r="G463" s="29"/>
       <c r="H463" s="48"/>
       <c r="I463" s="1" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="464" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -19952,7 +19961,7 @@
       <c r="G464" s="29"/>
       <c r="H464" s="53"/>
       <c r="I464" s="1" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="465" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -19975,7 +19984,7 @@
       <c r="G465" s="29"/>
       <c r="H465" s="48"/>
       <c r="I465" s="1" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="466" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -19998,7 +20007,7 @@
       <c r="G466" s="29"/>
       <c r="H466" s="48"/>
       <c r="I466" s="1" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="467" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20020,7 +20029,7 @@
       </c>
       <c r="G467" s="8"/>
       <c r="H467" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>656</v>
@@ -20039,7 +20048,7 @@
       <c r="F468" s="2"/>
       <c r="G468" s="28"/>
       <c r="H468" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>656</v>
@@ -20059,7 +20068,7 @@
       <c r="G469" s="28"/>
       <c r="H469" s="48"/>
       <c r="I469" s="58" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="470" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -20078,7 +20087,7 @@
       <c r="G470" s="27"/>
       <c r="H470" s="48"/>
       <c r="I470" s="1" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="471" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -20101,7 +20110,7 @@
       <c r="G471" s="27"/>
       <c r="H471" s="48"/>
       <c r="I471" s="1" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="472" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -20124,7 +20133,7 @@
       <c r="G472" s="27"/>
       <c r="H472" s="48"/>
       <c r="I472" s="1" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="473" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20147,7 +20156,7 @@
       <c r="G473" s="27"/>
       <c r="H473" s="48"/>
       <c r="I473" s="1" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="474" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20170,7 +20179,7 @@
       <c r="G474" s="27"/>
       <c r="H474" s="48"/>
       <c r="I474" s="1" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="475" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -20193,7 +20202,7 @@
       <c r="G475" s="27"/>
       <c r="H475" s="48"/>
       <c r="I475" s="1" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="476" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20216,7 +20225,7 @@
       <c r="G476" s="27"/>
       <c r="H476" s="48"/>
       <c r="I476" s="1" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="477" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -20239,7 +20248,7 @@
       <c r="G477" s="27"/>
       <c r="H477" s="48"/>
       <c r="I477" s="1" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="478" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -20262,7 +20271,7 @@
       <c r="G478" s="27"/>
       <c r="H478" s="48"/>
       <c r="I478" s="1" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="479" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20285,7 +20294,7 @@
       <c r="G479" s="27"/>
       <c r="H479" s="48"/>
       <c r="I479" s="1" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="480" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20301,7 +20310,7 @@
       <c r="F480" s="2"/>
       <c r="G480" s="27"/>
       <c r="H480" s="48" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>656</v>
@@ -20327,7 +20336,7 @@
       <c r="G481" s="27"/>
       <c r="H481" s="48"/>
       <c r="I481" s="1" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="482" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20350,7 +20359,7 @@
       <c r="G482" s="27"/>
       <c r="H482" s="48"/>
       <c r="I482" s="1" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="483" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20366,7 +20375,7 @@
       <c r="F483" s="2"/>
       <c r="G483" s="27"/>
       <c r="H483" s="48" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="I483" s="1" t="s">
         <v>656</v>
@@ -20392,7 +20401,7 @@
       <c r="G484" s="27"/>
       <c r="H484" s="48"/>
       <c r="I484" s="1" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="485" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20408,7 +20417,7 @@
       <c r="F485" s="2"/>
       <c r="G485" s="27"/>
       <c r="H485" s="48" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>656</v>
@@ -20434,7 +20443,7 @@
       <c r="G486" s="27"/>
       <c r="H486" s="48"/>
       <c r="I486" s="1" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="487" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20457,7 +20466,7 @@
       <c r="G487" s="27"/>
       <c r="H487" s="48"/>
       <c r="I487" s="1" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="488" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20480,7 +20489,7 @@
       <c r="G488" s="27"/>
       <c r="H488" s="48"/>
       <c r="I488" s="1" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="489" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20496,7 +20505,7 @@
       <c r="F489" s="2"/>
       <c r="G489" s="27"/>
       <c r="H489" s="48" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="I489" s="1" t="s">
         <v>656</v>
@@ -20522,7 +20531,7 @@
       <c r="G490" s="27"/>
       <c r="H490" s="48"/>
       <c r="I490" s="1" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="491" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20545,7 +20554,7 @@
       <c r="G491" s="27"/>
       <c r="H491" s="48"/>
       <c r="I491" s="1" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="492" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20568,7 +20577,7 @@
       <c r="G492" s="27"/>
       <c r="H492" s="48"/>
       <c r="I492" s="1" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="493" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20584,7 +20593,7 @@
       <c r="F493" s="2"/>
       <c r="G493" s="27"/>
       <c r="H493" s="48" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="I493" s="1" t="s">
         <v>656</v>
@@ -20610,7 +20619,7 @@
       <c r="G494" s="27"/>
       <c r="H494" s="48"/>
       <c r="I494" s="1" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="495" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20633,7 +20642,7 @@
       <c r="G495" s="27"/>
       <c r="H495" s="48"/>
       <c r="I495" s="1" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="496" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20649,7 +20658,7 @@
       <c r="F496" s="2"/>
       <c r="G496" s="27"/>
       <c r="H496" s="48" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="I496" s="1" t="s">
         <v>656</v>
@@ -20675,7 +20684,7 @@
       <c r="G497" s="27"/>
       <c r="H497" s="48"/>
       <c r="I497" s="1" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="498" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20691,7 +20700,7 @@
       <c r="F498" s="2"/>
       <c r="G498" s="27"/>
       <c r="H498" s="48" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="I498" s="1" t="s">
         <v>656</v>
@@ -20717,7 +20726,7 @@
       <c r="G499" s="27"/>
       <c r="H499" s="48"/>
       <c r="I499" s="1" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="500" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -20739,7 +20748,7 @@
       </c>
       <c r="G500" s="8"/>
       <c r="H500" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="I500" s="1" t="s">
         <v>656</v>
@@ -20758,7 +20767,7 @@
       <c r="F501" s="2"/>
       <c r="G501" s="28"/>
       <c r="H501" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I501" s="1" t="s">
         <v>656</v>
@@ -20778,7 +20787,7 @@
       <c r="G502" s="28"/>
       <c r="H502" s="48"/>
       <c r="I502" s="58" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="503" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -20797,7 +20806,7 @@
       <c r="G503" s="29"/>
       <c r="H503" s="48"/>
       <c r="I503" s="1" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="504" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20820,7 +20829,7 @@
       <c r="G504" s="29"/>
       <c r="H504" s="48"/>
       <c r="I504" s="1" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="505" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -20843,7 +20852,7 @@
       <c r="G505" s="29"/>
       <c r="H505" s="48"/>
       <c r="I505" s="1" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="506" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20866,7 +20875,7 @@
       <c r="G506" s="29"/>
       <c r="H506" s="48"/>
       <c r="I506" s="1" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="507" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20889,7 +20898,7 @@
       <c r="G507" s="29"/>
       <c r="H507" s="48"/>
       <c r="I507" s="1" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="508" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -20912,7 +20921,7 @@
       <c r="G508" s="29"/>
       <c r="H508" s="48"/>
       <c r="I508" s="1" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="509" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -20935,7 +20944,7 @@
       <c r="G509" s="29"/>
       <c r="H509" s="48"/>
       <c r="I509" s="1" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="510" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -20958,7 +20967,7 @@
       <c r="G510" s="29"/>
       <c r="H510" s="48"/>
       <c r="I510" s="1" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="511" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -20981,7 +20990,7 @@
       <c r="G511" s="29"/>
       <c r="H511" s="48"/>
       <c r="I511" s="1" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="512" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -21004,7 +21013,7 @@
       <c r="G512" s="29"/>
       <c r="H512" s="48"/>
       <c r="I512" s="1" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="513" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21020,7 +21029,7 @@
       <c r="F513" s="2"/>
       <c r="G513" s="29"/>
       <c r="H513" s="48" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>656</v>
@@ -21046,7 +21055,7 @@
       <c r="G514" s="29"/>
       <c r="H514" s="48"/>
       <c r="I514" s="1" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="515" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -21069,7 +21078,7 @@
       <c r="G515" s="29"/>
       <c r="H515" s="48"/>
       <c r="I515" s="1" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="516" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21085,7 +21094,7 @@
       <c r="F516" s="2"/>
       <c r="G516" s="29"/>
       <c r="H516" s="48" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>656</v>
@@ -21111,7 +21120,7 @@
       <c r="G517" s="29"/>
       <c r="H517" s="48"/>
       <c r="I517" s="1" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="518" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21127,7 +21136,7 @@
       <c r="F518" s="2"/>
       <c r="G518" s="29"/>
       <c r="H518" s="48" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>656</v>
@@ -21153,7 +21162,7 @@
       <c r="G519" s="29"/>
       <c r="H519" s="48"/>
       <c r="I519" s="1" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="520" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -21176,7 +21185,7 @@
       <c r="G520" s="29"/>
       <c r="H520" s="48"/>
       <c r="I520" s="1" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="521" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21192,7 +21201,7 @@
       <c r="F521" s="2"/>
       <c r="G521" s="29"/>
       <c r="H521" s="48" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="I521" s="1" t="s">
         <v>656</v>
@@ -21218,7 +21227,7 @@
       <c r="G522" s="29"/>
       <c r="H522" s="48"/>
       <c r="I522" s="1" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="523" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -21241,7 +21250,7 @@
       <c r="G523" s="29"/>
       <c r="H523" s="48"/>
       <c r="I523" s="1" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="524" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21257,7 +21266,7 @@
       <c r="F524" s="2"/>
       <c r="G524" s="29"/>
       <c r="H524" s="48" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="I524" s="1" t="s">
         <v>656</v>
@@ -21283,7 +21292,7 @@
       <c r="G525" s="29"/>
       <c r="H525" s="48"/>
       <c r="I525" s="1" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="526" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21306,7 +21315,7 @@
       <c r="G526" s="29"/>
       <c r="H526" s="48"/>
       <c r="I526" s="1" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="527" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21322,7 +21331,7 @@
       <c r="F527" s="2"/>
       <c r="G527" s="29"/>
       <c r="H527" s="48" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="I527" s="1" t="s">
         <v>656</v>
@@ -21348,7 +21357,7 @@
       <c r="G528" s="29"/>
       <c r="H528" s="48"/>
       <c r="I528" s="1" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="529" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21364,7 +21373,7 @@
       <c r="F529" s="2"/>
       <c r="G529" s="29"/>
       <c r="H529" s="48" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="I529" s="1" t="s">
         <v>656</v>
@@ -21390,7 +21399,7 @@
       <c r="G530" s="29"/>
       <c r="H530" s="48"/>
       <c r="I530" s="1" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="531" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -21406,7 +21415,7 @@
       <c r="F531" s="2"/>
       <c r="G531" s="29"/>
       <c r="H531" s="48" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="I531" s="1" t="s">
         <v>656</v>
@@ -21426,7 +21435,7 @@
       <c r="G532" s="29"/>
       <c r="H532" s="48"/>
       <c r="I532" s="1" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="533" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -21449,7 +21458,7 @@
       <c r="G533" s="29"/>
       <c r="H533" s="48"/>
       <c r="I533" s="1" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="534" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21465,7 +21474,7 @@
       <c r="F534" s="2"/>
       <c r="G534" s="29"/>
       <c r="H534" s="48" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="I534" s="1" t="s">
         <v>656</v>
@@ -21491,7 +21500,7 @@
       <c r="G535" s="29"/>
       <c r="H535" s="48"/>
       <c r="I535" s="1" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="536" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -21514,7 +21523,7 @@
       <c r="G536" s="29"/>
       <c r="H536" s="48"/>
       <c r="I536" s="48" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="537" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21536,7 +21545,7 @@
       </c>
       <c r="G537" s="19"/>
       <c r="H537" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="I537" s="1" t="s">
         <v>656</v>
@@ -21561,7 +21570,7 @@
       </c>
       <c r="G538" s="8"/>
       <c r="H538" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="I538" s="1" t="s">
         <v>656</v>
@@ -21600,7 +21609,7 @@
       <c r="G540" s="28"/>
       <c r="H540" s="53"/>
       <c r="I540" s="58" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="541" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -21623,7 +21632,7 @@
       <c r="G541" s="29"/>
       <c r="H541" s="48"/>
       <c r="I541" s="1" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="542" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21639,7 +21648,7 @@
       <c r="F542" s="2"/>
       <c r="G542" s="29"/>
       <c r="H542" s="48" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="I542" s="1" t="s">
         <v>656</v>
@@ -21665,7 +21674,7 @@
       <c r="G543" s="29"/>
       <c r="H543" s="48"/>
       <c r="I543" s="1" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="544" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21681,7 +21690,7 @@
       <c r="F544" s="2"/>
       <c r="G544" s="29"/>
       <c r="H544" s="48" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="I544" s="1" t="s">
         <v>656</v>
@@ -21707,7 +21716,7 @@
       <c r="G545" s="29"/>
       <c r="H545" s="48"/>
       <c r="I545" s="1" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="546" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21723,7 +21732,7 @@
       <c r="F546" s="2"/>
       <c r="G546" s="29"/>
       <c r="H546" s="48" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="I546" s="1" t="s">
         <v>656</v>
@@ -21749,7 +21758,7 @@
       <c r="G547" s="29"/>
       <c r="H547" s="48"/>
       <c r="I547" s="1" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="548" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21765,7 +21774,7 @@
       <c r="F548" s="2"/>
       <c r="G548" s="29"/>
       <c r="H548" s="48" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="I548" s="1" t="s">
         <v>656</v>
@@ -21791,7 +21800,7 @@
       <c r="G549" s="29"/>
       <c r="H549" s="48"/>
       <c r="I549" s="1" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="550" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21813,7 +21822,7 @@
       </c>
       <c r="G550" s="8"/>
       <c r="H550" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="I550" s="1" t="s">
         <v>656</v>
@@ -21852,7 +21861,7 @@
       <c r="G552" s="28"/>
       <c r="H552" s="48"/>
       <c r="I552" s="58" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="553" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21871,7 +21880,7 @@
       <c r="G553" s="2"/>
       <c r="H553" s="48"/>
       <c r="I553" s="1" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="554" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21894,7 +21903,7 @@
       <c r="G554" s="29"/>
       <c r="H554" s="48"/>
       <c r="I554" s="1" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="555" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21917,7 +21926,7 @@
       <c r="G555" s="29"/>
       <c r="H555" s="48"/>
       <c r="I555" s="1" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="556" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -21940,7 +21949,7 @@
       <c r="G556" s="29"/>
       <c r="H556" s="48"/>
       <c r="I556" s="1" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="557" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -21963,7 +21972,7 @@
       <c r="G557" s="29"/>
       <c r="H557" s="48"/>
       <c r="I557" s="1" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="558" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -21986,7 +21995,7 @@
       <c r="G558" s="29"/>
       <c r="H558" s="48"/>
       <c r="I558" s="1" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="559" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22009,7 +22018,7 @@
       <c r="G559" s="29"/>
       <c r="H559" s="48"/>
       <c r="I559" s="1" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="560" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22032,7 +22041,7 @@
       <c r="G560" s="29"/>
       <c r="H560" s="48"/>
       <c r="I560" s="1" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="561" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22055,7 +22064,7 @@
       <c r="G561" s="29"/>
       <c r="H561" s="48"/>
       <c r="I561" s="1" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="562" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -22078,7 +22087,7 @@
       <c r="G562" s="29"/>
       <c r="H562" s="48"/>
       <c r="I562" s="1" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="563" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22100,7 +22109,7 @@
       </c>
       <c r="G563" s="8"/>
       <c r="H563" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="I563" s="1" t="s">
         <v>656</v>
@@ -22139,7 +22148,7 @@
       <c r="G565" s="28"/>
       <c r="H565" s="48"/>
       <c r="I565" s="58" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="566" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22158,7 +22167,7 @@
       <c r="G566" s="29"/>
       <c r="H566" s="48"/>
       <c r="I566" s="1" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="567" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22181,7 +22190,7 @@
       <c r="G567" s="29"/>
       <c r="H567" s="48"/>
       <c r="I567" s="1" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="568" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22204,7 +22213,7 @@
       <c r="G568" s="29"/>
       <c r="H568" s="48"/>
       <c r="I568" s="1" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="569" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22227,7 +22236,7 @@
       <c r="G569" s="29"/>
       <c r="H569" s="48"/>
       <c r="I569" s="1" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="570" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22250,7 +22259,7 @@
       <c r="G570" s="29"/>
       <c r="H570" s="48"/>
       <c r="I570" s="1" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="571" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22273,7 +22282,7 @@
       <c r="G571" s="29"/>
       <c r="H571" s="48"/>
       <c r="I571" s="1" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="572" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22296,7 +22305,7 @@
       <c r="G572" s="29"/>
       <c r="H572" s="48"/>
       <c r="I572" s="1" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="573" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22312,7 +22321,7 @@
       <c r="F573" s="2"/>
       <c r="G573" s="29"/>
       <c r="H573" s="48" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="I573" s="1" t="s">
         <v>656</v>
@@ -22338,7 +22347,7 @@
       <c r="G574" s="29"/>
       <c r="H574" s="48"/>
       <c r="I574" s="1" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="575" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22361,7 +22370,7 @@
       <c r="G575" s="29"/>
       <c r="H575" s="48"/>
       <c r="I575" s="1" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="576" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22384,7 +22393,7 @@
       <c r="G576" s="29"/>
       <c r="H576" s="48"/>
       <c r="I576" s="1" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="577" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22400,7 +22409,7 @@
       <c r="F577" s="2"/>
       <c r="G577" s="29"/>
       <c r="H577" s="48" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="I577" s="1" t="s">
         <v>656</v>
@@ -22426,7 +22435,7 @@
       <c r="G578" s="29"/>
       <c r="H578" s="48"/>
       <c r="I578" s="1" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="579" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22442,7 +22451,7 @@
       <c r="F579" s="2"/>
       <c r="G579" s="29"/>
       <c r="H579" s="48" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="I579" s="1" t="s">
         <v>656</v>
@@ -22468,7 +22477,7 @@
       <c r="G580" s="29"/>
       <c r="H580" s="48"/>
       <c r="I580" s="1" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="581" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22484,7 +22493,7 @@
       <c r="F581" s="2"/>
       <c r="G581" s="29"/>
       <c r="H581" s="48" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="I581" s="1" t="s">
         <v>656</v>
@@ -22510,7 +22519,7 @@
       <c r="G582" s="29"/>
       <c r="H582" s="48"/>
       <c r="I582" s="1" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="583" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22526,7 +22535,7 @@
       <c r="F583" s="2"/>
       <c r="G583" s="29"/>
       <c r="H583" s="48" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="I583" s="1" t="s">
         <v>656</v>
@@ -22552,7 +22561,7 @@
       <c r="G584" s="29"/>
       <c r="H584" s="48"/>
       <c r="I584" s="1" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="585" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22574,7 +22583,7 @@
       </c>
       <c r="G585" s="8"/>
       <c r="H585" s="1" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="I585" s="1" t="s">
         <v>656</v>
@@ -22613,7 +22622,7 @@
       <c r="G587" s="28"/>
       <c r="H587" s="48"/>
       <c r="I587" s="58" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="588" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22632,7 +22641,7 @@
       <c r="G588" s="2"/>
       <c r="H588" s="48"/>
       <c r="I588" s="1" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="589" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -22655,7 +22664,7 @@
       <c r="G589" s="29"/>
       <c r="H589" s="48"/>
       <c r="I589" s="1" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="590" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -22678,7 +22687,7 @@
       <c r="G590" s="29"/>
       <c r="H590" s="48"/>
       <c r="I590" s="1" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="591" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22701,7 +22710,7 @@
       <c r="G591" s="29"/>
       <c r="H591" s="48"/>
       <c r="I591" s="1" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="592" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22717,7 +22726,7 @@
       <c r="F592" s="2"/>
       <c r="G592" s="29"/>
       <c r="H592" s="48" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="I592" s="1" t="s">
         <v>656</v>
@@ -22743,7 +22752,7 @@
       <c r="G593" s="29"/>
       <c r="H593" s="48"/>
       <c r="I593" s="1" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="594" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22759,7 +22768,7 @@
       <c r="F594" s="2"/>
       <c r="G594" s="29"/>
       <c r="H594" s="48" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="I594" s="1" t="s">
         <v>656</v>
@@ -22785,7 +22794,7 @@
       <c r="G595" s="29"/>
       <c r="H595" s="48"/>
       <c r="I595" s="1" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="596" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22801,7 +22810,7 @@
       <c r="F596" s="2"/>
       <c r="G596" s="29"/>
       <c r="H596" s="48" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="I596" s="1" t="s">
         <v>656</v>
@@ -22827,7 +22836,7 @@
       <c r="G597" s="29"/>
       <c r="H597" s="48"/>
       <c r="I597" s="1" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="598" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22843,7 +22852,7 @@
       <c r="F598" s="2"/>
       <c r="G598" s="29"/>
       <c r="H598" s="48" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="I598" s="1" t="s">
         <v>656</v>
@@ -22869,7 +22878,7 @@
       <c r="G599" s="29"/>
       <c r="H599" s="48"/>
       <c r="I599" s="58" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="600" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -22891,7 +22900,7 @@
       </c>
       <c r="G600" s="8"/>
       <c r="H600" s="1" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="I600" s="1" t="s">
         <v>656</v>
@@ -22930,7 +22939,7 @@
       <c r="G602" s="28"/>
       <c r="H602" s="48"/>
       <c r="I602" s="58" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="603" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -22949,7 +22958,7 @@
       <c r="G603" s="2"/>
       <c r="H603" s="48"/>
       <c r="I603" s="1" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="604" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -22972,7 +22981,7 @@
       <c r="G604" s="29"/>
       <c r="H604" s="48"/>
       <c r="I604" s="1" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="605" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -22995,7 +23004,7 @@
       <c r="G605" s="29"/>
       <c r="H605" s="48"/>
       <c r="I605" s="1" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="606" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -23018,7 +23027,7 @@
       <c r="G606" s="29"/>
       <c r="H606" s="48"/>
       <c r="I606" s="1" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="607" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -23041,7 +23050,7 @@
       <c r="G607" s="29"/>
       <c r="H607" s="48"/>
       <c r="I607" s="1" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="608" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -23064,7 +23073,7 @@
       <c r="G608" s="29"/>
       <c r="H608" s="48"/>
       <c r="I608" s="1" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="609" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23080,7 +23089,7 @@
       <c r="F609" s="2"/>
       <c r="G609" s="29"/>
       <c r="H609" s="48" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="I609" s="1" t="s">
         <v>656</v>
@@ -23106,7 +23115,7 @@
       <c r="G610" s="29"/>
       <c r="H610" s="48"/>
       <c r="I610" s="1" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="611" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -23129,7 +23138,7 @@
       <c r="G611" s="29"/>
       <c r="H611" s="48"/>
       <c r="I611" s="1" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="612" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -23152,7 +23161,7 @@
       <c r="G612" s="29"/>
       <c r="H612" s="48"/>
       <c r="I612" s="1" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="613" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23173,9 +23182,10 @@
         <v>656</v>
       </c>
       <c r="G613" s="8"/>
-      <c r="I613" s="1" t="s">
-        <v>2471</v>
-      </c>
+      <c r="H613" s="8" t="s">
+        <v>2470</v>
+      </c>
+      <c r="I613" s="8"/>
     </row>
     <row r="614" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A614" s="10"/>
@@ -23189,7 +23199,9 @@
       <c r="E614" s="27"/>
       <c r="F614" s="2"/>
       <c r="G614" s="28"/>
-      <c r="H614" s="48"/>
+      <c r="H614" s="48" t="s">
+        <v>2252</v>
+      </c>
       <c r="I614" s="1" t="s">
         <v>656</v>
       </c>
@@ -23208,7 +23220,7 @@
       <c r="G615" s="28"/>
       <c r="H615" s="48"/>
       <c r="I615" s="58" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="616" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -23231,7 +23243,7 @@
       <c r="G616" s="29"/>
       <c r="H616" s="48"/>
       <c r="I616" s="1" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="617" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -23254,7 +23266,7 @@
       <c r="G617" s="29"/>
       <c r="H617" s="48"/>
       <c r="I617" s="1" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="618" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23277,7 +23289,7 @@
       <c r="G618" s="29"/>
       <c r="H618" s="48"/>
       <c r="I618" s="1" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="619" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -23300,7 +23312,7 @@
       <c r="G619" s="29"/>
       <c r="H619" s="48"/>
       <c r="I619" s="1" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="620" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -23323,7 +23335,7 @@
       <c r="G620" s="29"/>
       <c r="H620" s="48"/>
       <c r="I620" s="1" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="621" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23339,7 +23351,7 @@
       <c r="F621" s="2"/>
       <c r="G621" s="29"/>
       <c r="H621" s="48" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="I621" s="1" t="s">
         <v>656</v>
@@ -23365,7 +23377,7 @@
       <c r="G622" s="29"/>
       <c r="H622" s="48"/>
       <c r="I622" s="1" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="623" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23381,7 +23393,7 @@
       <c r="F623" s="2"/>
       <c r="G623" s="29"/>
       <c r="H623" s="48" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="I623" s="1" t="s">
         <v>656</v>
@@ -23407,7 +23419,7 @@
       <c r="G624" s="29"/>
       <c r="H624" s="48"/>
       <c r="I624" s="1" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="625" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23423,7 +23435,7 @@
       <c r="F625" s="2"/>
       <c r="G625" s="29"/>
       <c r="H625" s="48" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="I625" s="1" t="s">
         <v>656</v>
@@ -23449,7 +23461,7 @@
       <c r="G626" s="29"/>
       <c r="H626" s="48"/>
       <c r="I626" s="1" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="627" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23465,7 +23477,7 @@
       <c r="F627" s="2"/>
       <c r="G627" s="29"/>
       <c r="H627" s="48" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="I627" s="1" t="s">
         <v>656</v>
@@ -23491,7 +23503,7 @@
       <c r="G628" s="29"/>
       <c r="H628" s="48"/>
       <c r="I628" s="1" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="629" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -23507,7 +23519,7 @@
       <c r="F629" s="2"/>
       <c r="G629" s="29"/>
       <c r="H629" s="48" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="I629" s="1" t="s">
         <v>656</v>
@@ -23533,7 +23545,7 @@
       <c r="G630" s="29"/>
       <c r="H630" s="48"/>
       <c r="I630" s="1" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="631" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -23556,7 +23568,7 @@
       <c r="G631" s="29"/>
       <c r="H631" s="48"/>
       <c r="I631" s="1" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="632" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23578,7 +23590,7 @@
       </c>
       <c r="G632" s="8"/>
       <c r="H632" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="I632" s="1" t="s">
         <v>656</v>
@@ -23617,7 +23629,7 @@
       <c r="G634" s="28"/>
       <c r="H634" s="48"/>
       <c r="I634" s="58" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="635" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -23640,7 +23652,7 @@
       <c r="G635" s="29"/>
       <c r="H635" s="48"/>
       <c r="I635" s="1" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="636" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -23663,7 +23675,7 @@
       <c r="G636" s="29"/>
       <c r="H636" s="48"/>
       <c r="I636" s="1" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="637" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23679,7 +23691,7 @@
       <c r="F637" s="2"/>
       <c r="G637" s="29"/>
       <c r="H637" s="48" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="I637" s="1" t="s">
         <v>656</v>
@@ -23705,7 +23717,7 @@
       <c r="G638" s="29"/>
       <c r="H638" s="48"/>
       <c r="I638" s="1" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="639" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23721,7 +23733,7 @@
       <c r="F639" s="2"/>
       <c r="G639" s="29"/>
       <c r="H639" s="48" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="I639" s="1" t="s">
         <v>656</v>
@@ -23741,7 +23753,7 @@
       <c r="G640" s="29"/>
       <c r="H640" s="48"/>
       <c r="I640" s="1" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="641" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -23764,7 +23776,7 @@
       <c r="G641" s="29"/>
       <c r="H641" s="48"/>
       <c r="I641" s="1" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="642" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -23787,7 +23799,7 @@
       <c r="G642" s="29"/>
       <c r="H642" s="48"/>
       <c r="I642" s="1" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="643" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -23810,7 +23822,7 @@
       <c r="G643" s="29"/>
       <c r="H643" s="48"/>
       <c r="I643" s="1" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="644" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -23833,7 +23845,7 @@
       <c r="G644" s="29"/>
       <c r="H644" s="48"/>
       <c r="I644" s="48" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="645" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23849,7 +23861,7 @@
       <c r="F645" s="2"/>
       <c r="G645" s="29"/>
       <c r="H645" s="48" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="I645" s="1" t="s">
         <v>656</v>
@@ -23869,7 +23881,7 @@
       <c r="G646" s="29"/>
       <c r="H646" s="48"/>
       <c r="I646" s="1" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="647" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -23892,7 +23904,7 @@
       <c r="G647" s="29"/>
       <c r="H647" s="48"/>
       <c r="I647" s="1" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="648" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -23915,7 +23927,7 @@
       <c r="G648" s="29"/>
       <c r="H648" s="48"/>
       <c r="I648" s="1" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="649" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23931,7 +23943,7 @@
       <c r="F649" s="2"/>
       <c r="G649" s="29"/>
       <c r="H649" s="48" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="I649" s="1" t="s">
         <v>656</v>
@@ -23957,7 +23969,7 @@
       <c r="G650" s="29"/>
       <c r="H650" s="48"/>
       <c r="I650" s="1" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="651" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -23979,7 +23991,7 @@
       </c>
       <c r="G651" s="8"/>
       <c r="H651" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="I651" s="1" t="s">
         <v>656</v>
@@ -23998,7 +24010,7 @@
       <c r="F652" s="2"/>
       <c r="G652" s="28"/>
       <c r="H652" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I652" s="1" t="s">
         <v>656</v>
@@ -24018,7 +24030,7 @@
       <c r="G653" s="28"/>
       <c r="H653" s="48"/>
       <c r="I653" s="58" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="654" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24037,7 +24049,7 @@
       <c r="G654" s="2"/>
       <c r="H654" s="48"/>
       <c r="I654" s="1" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="655" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -24060,7 +24072,7 @@
       <c r="G655" s="29"/>
       <c r="H655" s="48"/>
       <c r="I655" s="1" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="656" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24083,7 +24095,7 @@
       <c r="G656" s="29"/>
       <c r="H656" s="48"/>
       <c r="I656" s="1" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="657" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24099,7 +24111,7 @@
       <c r="F657" s="2"/>
       <c r="G657" s="29"/>
       <c r="H657" s="48" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="I657" s="1" t="s">
         <v>656</v>
@@ -24125,7 +24137,7 @@
       <c r="G658" s="29"/>
       <c r="H658" s="48"/>
       <c r="I658" s="1" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="659" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24141,7 +24153,7 @@
       <c r="F659" s="2"/>
       <c r="G659" s="29"/>
       <c r="H659" s="48" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="I659" s="1" t="s">
         <v>656</v>
@@ -24167,7 +24179,7 @@
       <c r="G660" s="29"/>
       <c r="H660" s="48"/>
       <c r="I660" s="1" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="661" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24183,7 +24195,7 @@
       <c r="F661" s="2"/>
       <c r="G661" s="29"/>
       <c r="H661" s="48" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="I661" s="1" t="s">
         <v>656</v>
@@ -24209,7 +24221,7 @@
       <c r="G662" s="29"/>
       <c r="H662" s="48"/>
       <c r="I662" s="1" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="663" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24225,7 +24237,7 @@
       <c r="F663" s="2"/>
       <c r="G663" s="29"/>
       <c r="H663" s="48" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="I663" s="1" t="s">
         <v>656</v>
@@ -24251,7 +24263,7 @@
       <c r="G664" s="29"/>
       <c r="H664" s="48"/>
       <c r="I664" s="1" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="665" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24267,7 +24279,7 @@
       <c r="F665" s="2"/>
       <c r="G665" s="29"/>
       <c r="H665" s="48" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="I665" s="1" t="s">
         <v>656</v>
@@ -24293,7 +24305,7 @@
       <c r="G666" s="29"/>
       <c r="H666" s="48"/>
       <c r="I666" s="1" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="667" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -24316,7 +24328,7 @@
       <c r="G667" s="29"/>
       <c r="H667" s="48"/>
       <c r="I667" s="1" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="668" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24338,7 +24350,7 @@
       </c>
       <c r="G668" s="8"/>
       <c r="H668" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="I668" s="1" t="s">
         <v>656</v>
@@ -24377,7 +24389,7 @@
       <c r="G670" s="28"/>
       <c r="H670" s="48"/>
       <c r="I670" s="58" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="671" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -24396,7 +24408,7 @@
       <c r="G671" s="2"/>
       <c r="H671" s="48"/>
       <c r="I671" s="1" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="672" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -24419,7 +24431,7 @@
       <c r="G672" s="29"/>
       <c r="H672" s="48"/>
       <c r="I672" s="1" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="673" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -24442,7 +24454,7 @@
       <c r="G673" s="29"/>
       <c r="H673" s="48"/>
       <c r="I673" s="1" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="674" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -24465,7 +24477,7 @@
       <c r="G674" s="29"/>
       <c r="H674" s="48"/>
       <c r="I674" s="1" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="675" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24487,7 +24499,7 @@
       </c>
       <c r="G675" s="8"/>
       <c r="H675" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="I675" s="1" t="s">
         <v>656</v>
@@ -24526,7 +24538,7 @@
       <c r="G677" s="28"/>
       <c r="H677" s="48"/>
       <c r="I677" s="58" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="678" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -24549,7 +24561,7 @@
       <c r="G678" s="29"/>
       <c r="H678" s="48"/>
       <c r="I678" s="1" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="679" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24572,7 +24584,7 @@
       <c r="G679" s="29"/>
       <c r="H679" s="48"/>
       <c r="I679" s="1" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="680" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -24595,7 +24607,7 @@
       <c r="G680" s="29"/>
       <c r="H680" s="48"/>
       <c r="I680" s="1" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="681" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24611,7 +24623,7 @@
       <c r="F681" s="2"/>
       <c r="G681" s="29"/>
       <c r="H681" s="48" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="I681" s="1" t="s">
         <v>656</v>
@@ -24637,7 +24649,7 @@
       <c r="G682" s="29"/>
       <c r="H682" s="48"/>
       <c r="I682" s="1" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="683" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24653,7 +24665,7 @@
       <c r="F683" s="2"/>
       <c r="G683" s="29"/>
       <c r="H683" s="48" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="I683" s="1" t="s">
         <v>656</v>
@@ -24679,7 +24691,7 @@
       <c r="G684" s="29"/>
       <c r="H684" s="48"/>
       <c r="I684" s="1" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="685" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24701,7 +24713,7 @@
       </c>
       <c r="G685" s="19"/>
       <c r="H685" s="48" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="I685" s="1" t="s">
         <v>656</v>
@@ -24723,7 +24735,7 @@
       <c r="G686" s="2"/>
       <c r="H686" s="48"/>
       <c r="I686" s="1" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="687" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24745,7 +24757,7 @@
       </c>
       <c r="G687" s="8"/>
       <c r="H687" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="I687" s="1" t="s">
         <v>656</v>
@@ -24784,7 +24796,7 @@
       <c r="G689" s="28"/>
       <c r="H689" s="48"/>
       <c r="I689" s="58" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="690" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -24807,7 +24819,7 @@
       <c r="G690" s="29"/>
       <c r="H690" s="48"/>
       <c r="I690" s="1" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="691" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24829,7 +24841,7 @@
       </c>
       <c r="G691" s="8"/>
       <c r="H691" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="I691" s="1" t="s">
         <v>656</v>
@@ -24868,7 +24880,7 @@
       <c r="G693" s="28"/>
       <c r="H693" s="48"/>
       <c r="I693" s="58" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="694" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -24891,7 +24903,7 @@
       <c r="G694" s="29"/>
       <c r="H694" s="48"/>
       <c r="I694" s="1" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="695" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -24914,7 +24926,7 @@
       <c r="G695" s="29"/>
       <c r="H695" s="48"/>
       <c r="I695" s="1" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="696" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -24936,7 +24948,7 @@
       </c>
       <c r="G696" s="8"/>
       <c r="H696" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="I696" s="1" t="s">
         <v>656</v>
@@ -24975,7 +24987,7 @@
       <c r="G698" s="28"/>
       <c r="H698" s="48"/>
       <c r="I698" s="58" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="699" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -24998,7 +25010,7 @@
       <c r="G699" s="29"/>
       <c r="H699" s="48"/>
       <c r="I699" s="1" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="700" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -25021,7 +25033,7 @@
       <c r="G700" s="29"/>
       <c r="H700" s="48"/>
       <c r="I700" s="1" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="701" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -25044,7 +25056,7 @@
       <c r="G701" s="29"/>
       <c r="H701" s="48"/>
       <c r="I701" s="1" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="702" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25060,7 +25072,7 @@
       <c r="F702" s="2"/>
       <c r="G702" s="29"/>
       <c r="H702" s="48" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="I702" s="1" t="s">
         <v>656</v>
@@ -25086,7 +25098,7 @@
       <c r="G703" s="29"/>
       <c r="H703" s="48"/>
       <c r="I703" s="1" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="704" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -25109,7 +25121,7 @@
       <c r="G704" s="29"/>
       <c r="H704" s="48"/>
       <c r="I704" s="1" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="705" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25125,7 +25137,7 @@
       <c r="F705" s="2"/>
       <c r="G705" s="29"/>
       <c r="H705" s="48" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="I705" s="1" t="s">
         <v>656</v>
@@ -25151,7 +25163,7 @@
       <c r="G706" s="29"/>
       <c r="H706" s="48"/>
       <c r="I706" s="1" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="707" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25167,7 +25179,7 @@
       <c r="F707" s="2"/>
       <c r="G707" s="29"/>
       <c r="H707" s="48" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="I707" s="1" t="s">
         <v>656</v>
@@ -25193,7 +25205,7 @@
       <c r="G708" s="29"/>
       <c r="H708" s="48"/>
       <c r="I708" s="1" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="709" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25215,7 +25227,7 @@
       </c>
       <c r="G709" s="8"/>
       <c r="H709" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="I709" s="1" t="s">
         <v>656</v>
@@ -25254,7 +25266,7 @@
       <c r="G711" s="28"/>
       <c r="H711" s="48"/>
       <c r="I711" s="58" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="712" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -25273,7 +25285,7 @@
       <c r="G712" s="29"/>
       <c r="H712" s="48"/>
       <c r="I712" s="1" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="713" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -25296,7 +25308,7 @@
       <c r="G713" s="29"/>
       <c r="H713" s="48"/>
       <c r="I713" s="1" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="714" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -25319,7 +25331,7 @@
       <c r="G714" s="29"/>
       <c r="H714" s="48"/>
       <c r="I714" s="1" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="715" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25335,7 +25347,7 @@
       <c r="F715" s="2"/>
       <c r="G715" s="27"/>
       <c r="H715" s="48" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="I715" s="1" t="s">
         <v>656</v>
@@ -25361,7 +25373,7 @@
       <c r="G716" s="27"/>
       <c r="H716" s="48"/>
       <c r="I716" s="1" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="717" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25383,7 +25395,7 @@
       </c>
       <c r="G717" s="19"/>
       <c r="H717" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="I717" s="1" t="s">
         <v>656</v>
@@ -25408,7 +25420,7 @@
       </c>
       <c r="G718" s="8"/>
       <c r="H718" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="I718" s="1" t="s">
         <v>656</v>
@@ -25447,7 +25459,7 @@
       <c r="G720" s="28"/>
       <c r="H720" s="48"/>
       <c r="I720" s="58" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="721" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -25470,7 +25482,7 @@
       <c r="G721" s="29"/>
       <c r="H721" s="1"/>
       <c r="I721" s="1" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="722" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -25493,7 +25505,7 @@
       <c r="G722" s="29"/>
       <c r="H722" s="1"/>
       <c r="I722" s="1" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="723" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25516,7 +25528,7 @@
       <c r="G723" s="29"/>
       <c r="H723" s="1"/>
       <c r="I723" s="1" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="724" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25539,7 +25551,7 @@
       <c r="G724" s="29"/>
       <c r="H724" s="1"/>
       <c r="I724" s="1" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="725" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25562,7 +25574,7 @@
       <c r="G725" s="29"/>
       <c r="H725" s="1"/>
       <c r="I725" s="1" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="726" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25585,7 +25597,7 @@
       <c r="G726" s="29"/>
       <c r="H726" s="1"/>
       <c r="I726" s="1" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="727" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25601,7 +25613,7 @@
       <c r="F727" s="2"/>
       <c r="G727" s="29"/>
       <c r="H727" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="I727" s="1" t="s">
         <v>656</v>
@@ -25627,7 +25639,7 @@
       <c r="G728" s="29"/>
       <c r="H728" s="1"/>
       <c r="I728" s="1" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="729" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -25650,7 +25662,7 @@
       <c r="G729" s="29"/>
       <c r="H729" s="1"/>
       <c r="I729" s="1" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="730" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25666,7 +25678,7 @@
       <c r="F730" s="2"/>
       <c r="G730" s="29"/>
       <c r="H730" s="1" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="I730" s="1" t="s">
         <v>656</v>
@@ -25692,7 +25704,7 @@
       <c r="G731" s="29"/>
       <c r="H731" s="1"/>
       <c r="I731" s="1" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="732" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25714,7 +25726,7 @@
       </c>
       <c r="G732" s="19"/>
       <c r="H732" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="I732" s="1" t="s">
         <v>656</v>
@@ -25739,7 +25751,7 @@
       </c>
       <c r="G733" s="8"/>
       <c r="H733" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="I733" s="1" t="s">
         <v>656</v>
@@ -25778,7 +25790,7 @@
       <c r="G735" s="28"/>
       <c r="H735" s="48"/>
       <c r="I735" s="58" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="736" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -25801,7 +25813,7 @@
       <c r="G736" s="29"/>
       <c r="H736" s="1"/>
       <c r="I736" s="1" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="737" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25823,7 +25835,7 @@
       </c>
       <c r="G737" s="8"/>
       <c r="H737" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="I737" s="1" t="s">
         <v>656</v>
@@ -25862,7 +25874,7 @@
       <c r="G739" s="28"/>
       <c r="H739" s="48"/>
       <c r="I739" s="1" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="740" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -25881,7 +25893,7 @@
       <c r="G740" s="2"/>
       <c r="H740" s="1"/>
       <c r="I740" s="1" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="741" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -25904,7 +25916,7 @@
       <c r="G741" s="29"/>
       <c r="H741" s="1"/>
       <c r="I741" s="1" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="742" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -25927,7 +25939,7 @@
       <c r="G742" s="29"/>
       <c r="H742" s="1"/>
       <c r="I742" s="1" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="743" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -25950,7 +25962,7 @@
       <c r="G743" s="29"/>
       <c r="H743" s="1"/>
       <c r="I743" s="1" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="744" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -25973,7 +25985,7 @@
       <c r="G744" s="29"/>
       <c r="H744" s="1"/>
       <c r="I744" s="1" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="745" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -25996,7 +26008,7 @@
       <c r="G745" s="29"/>
       <c r="H745" s="1"/>
       <c r="I745" s="1" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="746" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26012,7 +26024,7 @@
       <c r="F746" s="2"/>
       <c r="G746" s="29"/>
       <c r="H746" s="1" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="I746" s="1" t="s">
         <v>656</v>
@@ -26038,7 +26050,7 @@
       <c r="G747" s="29"/>
       <c r="H747" s="1"/>
       <c r="I747" s="1" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="748" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26054,7 +26066,7 @@
       <c r="F748" s="2"/>
       <c r="G748" s="29"/>
       <c r="H748" s="1" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="I748" s="1" t="s">
         <v>656</v>
@@ -26080,7 +26092,7 @@
       <c r="G749" s="29"/>
       <c r="H749" s="48"/>
       <c r="I749" s="1" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="750" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26102,7 +26114,7 @@
       </c>
       <c r="G750" s="8"/>
       <c r="H750" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="I750" s="1" t="s">
         <v>656</v>
@@ -26141,7 +26153,7 @@
       <c r="G752" s="28"/>
       <c r="H752" s="48"/>
       <c r="I752" s="58" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="753" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -26164,7 +26176,7 @@
       <c r="G753" s="29"/>
       <c r="H753" s="1"/>
       <c r="I753" s="1" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="754" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26186,7 +26198,7 @@
       </c>
       <c r="G754" s="8"/>
       <c r="H754" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="I754" s="1" t="s">
         <v>656</v>
@@ -26225,7 +26237,7 @@
       <c r="G756" s="28"/>
       <c r="H756" s="48"/>
       <c r="I756" s="58" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="757" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -26248,7 +26260,7 @@
       <c r="G757" s="29"/>
       <c r="H757" s="1"/>
       <c r="I757" s="1" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="758" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26271,7 +26283,7 @@
       <c r="G758" s="29"/>
       <c r="H758" s="1"/>
       <c r="I758" s="1" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="759" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26294,7 +26306,7 @@
       <c r="G759" s="29"/>
       <c r="H759" s="1"/>
       <c r="I759" s="1" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="760" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26317,7 +26329,7 @@
       <c r="G760" s="29"/>
       <c r="H760" s="1"/>
       <c r="I760" s="1" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="761" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26340,7 +26352,7 @@
       <c r="G761" s="29"/>
       <c r="H761" s="1"/>
       <c r="I761" s="1" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="762" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26363,7 +26375,7 @@
       <c r="G762" s="29"/>
       <c r="H762" s="1"/>
       <c r="I762" s="1" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="763" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -26386,7 +26398,7 @@
       <c r="G763" s="29"/>
       <c r="H763" s="1"/>
       <c r="I763" s="1" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="764" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -26409,7 +26421,7 @@
       <c r="G764" s="29"/>
       <c r="H764" s="1"/>
       <c r="I764" s="1" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="765" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26425,7 +26437,7 @@
       <c r="F765" s="2"/>
       <c r="G765" s="29"/>
       <c r="H765" s="1" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="I765" s="1" t="s">
         <v>656</v>
@@ -26451,7 +26463,7 @@
       <c r="G766" s="29"/>
       <c r="H766" s="1"/>
       <c r="I766" s="1" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="767" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26473,7 +26485,7 @@
       </c>
       <c r="G767" s="19"/>
       <c r="H767" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="I767" s="1" t="s">
         <v>656</v>
@@ -26498,7 +26510,7 @@
       </c>
       <c r="G768" s="8"/>
       <c r="H768" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="I768" s="1" t="s">
         <v>656</v>
@@ -26537,7 +26549,7 @@
       <c r="G770" s="28"/>
       <c r="H770" s="48"/>
       <c r="I770" s="49" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="771" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26560,7 +26572,7 @@
       <c r="G771" s="29"/>
       <c r="H771" s="1"/>
       <c r="I771" s="1" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="772" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26576,7 +26588,7 @@
       <c r="F772" s="2"/>
       <c r="G772" s="29"/>
       <c r="H772" s="1" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="I772" s="1" t="s">
         <v>656</v>
@@ -26602,7 +26614,7 @@
       <c r="G773" s="29"/>
       <c r="H773" s="1"/>
       <c r="I773" s="1" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="774" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26618,7 +26630,7 @@
       <c r="F774" s="2"/>
       <c r="G774" s="29"/>
       <c r="H774" s="1" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="I774" s="1" t="s">
         <v>656</v>
@@ -26644,7 +26656,7 @@
       <c r="G775" s="29"/>
       <c r="H775" s="1"/>
       <c r="I775" s="1" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="776" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26660,7 +26672,7 @@
       <c r="F776" s="2"/>
       <c r="G776" s="29"/>
       <c r="H776" s="1" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="I776" s="1" t="s">
         <v>656</v>
@@ -26686,7 +26698,7 @@
       <c r="G777" s="29"/>
       <c r="H777" s="1"/>
       <c r="I777" s="1" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="778" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26708,7 +26720,7 @@
       </c>
       <c r="G778" s="8"/>
       <c r="H778" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="I778" s="1" t="s">
         <v>656</v>
@@ -26747,7 +26759,7 @@
       <c r="G780" s="28"/>
       <c r="H780" s="48"/>
       <c r="I780" s="58" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="781" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -26770,7 +26782,7 @@
       <c r="G781" s="29"/>
       <c r="H781" s="1"/>
       <c r="I781" s="1" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="782" spans="1:9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -26786,7 +26798,7 @@
       <c r="F782" s="2"/>
       <c r="G782" s="29"/>
       <c r="H782" s="1" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="I782" s="1" t="s">
         <v>656</v>
@@ -26812,7 +26824,7 @@
       <c r="G783" s="29"/>
       <c r="H783" s="1"/>
       <c r="I783" s="1" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="784" spans="1:9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -26828,7 +26840,7 @@
       <c r="F784" s="2"/>
       <c r="G784" s="29"/>
       <c r="H784" s="1" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="I784" s="1" t="s">
         <v>656</v>
@@ -26854,7 +26866,7 @@
       <c r="G785" s="29"/>
       <c r="H785" s="1"/>
       <c r="I785" s="1" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="786" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26876,7 +26888,7 @@
       </c>
       <c r="G786" s="8"/>
       <c r="H786" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="I786" s="1" t="s">
         <v>656</v>
@@ -26915,7 +26927,7 @@
       <c r="G788" s="28"/>
       <c r="H788" s="48"/>
       <c r="I788" s="58" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="789" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26938,7 +26950,7 @@
       <c r="G789" s="29"/>
       <c r="H789" s="1"/>
       <c r="I789" s="1" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="790" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26954,7 +26966,7 @@
       <c r="F790" s="2"/>
       <c r="G790" s="29"/>
       <c r="H790" s="1" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="I790" s="1" t="s">
         <v>656</v>
@@ -26980,7 +26992,7 @@
       <c r="G791" s="29"/>
       <c r="H791" s="1"/>
       <c r="I791" s="1" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="792" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -26996,7 +27008,7 @@
       <c r="F792" s="2"/>
       <c r="G792" s="29"/>
       <c r="H792" s="48" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="I792" s="1" t="s">
         <v>656</v>
@@ -27022,7 +27034,7 @@
       <c r="G793" s="29"/>
       <c r="H793" s="1"/>
       <c r="I793" s="1" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="794" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27038,7 +27050,7 @@
       <c r="F794" s="2"/>
       <c r="G794" s="29"/>
       <c r="H794" s="48" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="I794" s="1" t="s">
         <v>656</v>
@@ -27064,7 +27076,7 @@
       <c r="G795" s="29"/>
       <c r="H795" s="1"/>
       <c r="I795" s="1" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="796" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -27087,7 +27099,7 @@
       <c r="G796" s="29"/>
       <c r="H796" s="1"/>
       <c r="I796" s="1" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="797" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27103,7 +27115,7 @@
       <c r="F797" s="2"/>
       <c r="G797" s="29"/>
       <c r="H797" s="48" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="I797" s="1" t="s">
         <v>656</v>
@@ -27129,7 +27141,7 @@
       <c r="G798" s="29"/>
       <c r="H798" s="1"/>
       <c r="I798" s="1" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="799" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27145,7 +27157,7 @@
       <c r="F799" s="2"/>
       <c r="G799" s="29"/>
       <c r="H799" s="48" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="I799" s="1" t="s">
         <v>656</v>
@@ -27165,7 +27177,7 @@
       <c r="G800" s="29"/>
       <c r="H800" s="48"/>
       <c r="I800" s="1" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="801" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27188,7 +27200,7 @@
       <c r="G801" s="29"/>
       <c r="H801" s="1"/>
       <c r="I801" s="1" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="802" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -27211,7 +27223,7 @@
       <c r="G802" s="29"/>
       <c r="H802" s="1"/>
       <c r="I802" s="1" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="803" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27227,7 +27239,7 @@
       <c r="F803" s="2"/>
       <c r="G803" s="29"/>
       <c r="H803" s="48" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="I803" s="1" t="s">
         <v>656</v>
@@ -27247,7 +27259,7 @@
       <c r="G804" s="29"/>
       <c r="H804" s="48"/>
       <c r="I804" s="1" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="805" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27270,7 +27282,7 @@
       <c r="G805" s="29"/>
       <c r="H805" s="1"/>
       <c r="I805" s="1" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="806" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27293,7 +27305,7 @@
       <c r="G806" s="29"/>
       <c r="H806" s="1"/>
       <c r="I806" s="1" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="807" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27316,7 +27328,7 @@
       <c r="G807" s="29"/>
       <c r="H807" s="1"/>
       <c r="I807" s="1" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="808" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27332,7 +27344,7 @@
       <c r="F808" s="2"/>
       <c r="G808" s="29"/>
       <c r="H808" s="48" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="I808" s="1" t="s">
         <v>656</v>
@@ -27358,7 +27370,7 @@
       <c r="G809" s="29"/>
       <c r="H809" s="1"/>
       <c r="I809" s="1" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="810" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27380,7 +27392,7 @@
       </c>
       <c r="G810" s="24"/>
       <c r="H810" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="I810" s="1" t="s">
         <v>656</v>
@@ -27400,7 +27412,7 @@
       <c r="G811" s="29"/>
       <c r="H811" s="1"/>
       <c r="I811" s="1" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="812" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27422,7 +27434,7 @@
       </c>
       <c r="G812" s="19"/>
       <c r="H812" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="I812" s="1" t="s">
         <v>656</v>
@@ -27447,7 +27459,7 @@
       </c>
       <c r="G813" s="8"/>
       <c r="H813" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="I813" s="1" t="s">
         <v>656</v>
@@ -27486,7 +27498,7 @@
       <c r="G815" s="28"/>
       <c r="H815" s="48"/>
       <c r="I815" s="58" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="816" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -27509,7 +27521,7 @@
       <c r="G816" s="29"/>
       <c r="H816" s="1"/>
       <c r="I816" s="1" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="817" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -27532,7 +27544,7 @@
       <c r="G817" s="29"/>
       <c r="H817" s="1"/>
       <c r="I817" s="1" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="818" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27554,7 +27566,7 @@
       </c>
       <c r="G818" s="8"/>
       <c r="H818" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="I818" s="1" t="s">
         <v>656</v>
@@ -27572,7 +27584,9 @@
       <c r="E819" s="27"/>
       <c r="F819" s="2"/>
       <c r="G819" s="28"/>
-      <c r="H819" s="48"/>
+      <c r="H819" s="48" t="s">
+        <v>2252</v>
+      </c>
       <c r="I819" s="1" t="s">
         <v>656</v>
       </c>
@@ -27591,7 +27605,7 @@
       <c r="G820" s="28"/>
       <c r="H820" s="48"/>
       <c r="I820" s="48" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="821" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -27614,7 +27628,7 @@
       <c r="G821" s="29"/>
       <c r="H821" s="1"/>
       <c r="I821" s="1" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="822" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27636,7 +27650,7 @@
       </c>
       <c r="G822" s="8"/>
       <c r="H822" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="I822" s="1" t="s">
         <v>656</v>
@@ -27675,7 +27689,7 @@
       <c r="G824" s="28"/>
       <c r="H824" s="48"/>
       <c r="I824" s="58" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="825" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -27694,7 +27708,7 @@
       <c r="G825" s="29"/>
       <c r="H825" s="1"/>
       <c r="I825" s="1" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="826" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27717,7 +27731,7 @@
       <c r="G826" s="29"/>
       <c r="H826" s="1"/>
       <c r="I826" s="1" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="827" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27740,7 +27754,7 @@
       <c r="G827" s="29"/>
       <c r="H827" s="1"/>
       <c r="I827" s="1" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="828" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27763,7 +27777,7 @@
       <c r="G828" s="29"/>
       <c r="H828" s="1"/>
       <c r="I828" s="1" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="829" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27785,7 +27799,7 @@
       </c>
       <c r="G829" s="8"/>
       <c r="H829" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="I829" s="1" t="s">
         <v>656</v>
@@ -27824,7 +27838,7 @@
       <c r="G831" s="28"/>
       <c r="H831" s="48"/>
       <c r="I831" s="58" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="832" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -27847,7 +27861,7 @@
       <c r="G832" s="29"/>
       <c r="H832" s="48"/>
       <c r="I832" s="48" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="833" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27867,7 +27881,7 @@
       </c>
       <c r="G833" s="8"/>
       <c r="H833" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="I833" s="1" t="s">
         <v>656</v>
@@ -27906,7 +27920,7 @@
       <c r="G835" s="28"/>
       <c r="H835" s="48"/>
       <c r="I835" s="58" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="836" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -27929,7 +27943,7 @@
       <c r="G836" s="29"/>
       <c r="H836" s="1"/>
       <c r="I836" s="1" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="837" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -27951,7 +27965,7 @@
       </c>
       <c r="G837" s="8"/>
       <c r="H837" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="I837" s="1" t="s">
         <v>656</v>
@@ -27969,7 +27983,9 @@
       <c r="E838" s="27"/>
       <c r="F838" s="2"/>
       <c r="G838" s="28"/>
-      <c r="H838" s="48"/>
+      <c r="H838" s="48" t="s">
+        <v>2252</v>
+      </c>
       <c r="I838" s="1" t="s">
         <v>656</v>
       </c>
@@ -27988,7 +28004,7 @@
       <c r="G839" s="28"/>
       <c r="H839" s="48"/>
       <c r="I839" s="58" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="840" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28011,7 +28027,7 @@
       <c r="G840" s="29"/>
       <c r="H840" s="1"/>
       <c r="I840" s="1" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="841" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28033,7 +28049,7 @@
       </c>
       <c r="G841" s="8"/>
       <c r="H841" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="I841" s="1" t="s">
         <v>656</v>
@@ -28072,7 +28088,7 @@
       <c r="G843" s="28"/>
       <c r="H843" s="48"/>
       <c r="I843" s="58" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="844" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28097,7 +28113,7 @@
       </c>
       <c r="H844" s="1"/>
       <c r="I844" s="1" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="845" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28119,7 +28135,7 @@
       </c>
       <c r="G845" s="19"/>
       <c r="H845" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="I845" s="1" t="s">
         <v>656</v>
@@ -28144,7 +28160,7 @@
       </c>
       <c r="G846" s="8"/>
       <c r="H846" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="I846" s="1" t="s">
         <v>656</v>
@@ -28183,7 +28199,7 @@
       <c r="G848" s="28"/>
       <c r="H848" s="48"/>
       <c r="I848" s="58" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="849" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -28206,7 +28222,7 @@
       <c r="G849" s="29"/>
       <c r="H849" s="48"/>
       <c r="I849" s="1" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="850" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -28229,7 +28245,7 @@
       <c r="G850" s="29"/>
       <c r="H850" s="48"/>
       <c r="I850" s="1" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="851" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28245,7 +28261,7 @@
       <c r="F851" s="2"/>
       <c r="G851" s="29"/>
       <c r="H851" s="48" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="I851" s="1" t="s">
         <v>656</v>
@@ -28271,7 +28287,7 @@
       <c r="G852" s="29"/>
       <c r="H852" s="48"/>
       <c r="I852" s="1" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="853" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28293,7 +28309,7 @@
       </c>
       <c r="G853" s="8"/>
       <c r="H853" s="50" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="I853" s="1" t="s">
         <v>656</v>
@@ -28332,7 +28348,7 @@
       <c r="G855" s="28"/>
       <c r="H855" s="53"/>
       <c r="I855" s="65" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="856" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28351,7 +28367,7 @@
       <c r="G856" s="2"/>
       <c r="H856" s="50"/>
       <c r="I856" s="1" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="857" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28374,7 +28390,7 @@
       <c r="G857" s="29"/>
       <c r="H857" s="50"/>
       <c r="I857" s="1" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="858" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28397,7 +28413,7 @@
       <c r="G858" s="29"/>
       <c r="H858" s="50"/>
       <c r="I858" s="1" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="859" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -28420,7 +28436,7 @@
       <c r="G859" s="29"/>
       <c r="H859" s="53"/>
       <c r="I859" s="1" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="860" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28439,7 +28455,7 @@
       <c r="G860" s="29"/>
       <c r="H860" s="50"/>
       <c r="I860" s="1" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="861" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28462,7 +28478,7 @@
       <c r="G861" s="29"/>
       <c r="H861" s="50"/>
       <c r="I861" s="1" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="862" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28485,7 +28501,7 @@
       <c r="G862" s="29"/>
       <c r="H862" s="50"/>
       <c r="I862" s="1" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="863" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28501,7 +28517,7 @@
       <c r="F863" s="2"/>
       <c r="G863" s="29"/>
       <c r="H863" s="50" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="I863" s="1" t="s">
         <v>656</v>
@@ -28527,7 +28543,7 @@
       <c r="G864" s="29"/>
       <c r="H864" s="50"/>
       <c r="I864" s="1" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="865" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28549,7 +28565,7 @@
       </c>
       <c r="G865" s="8"/>
       <c r="H865" s="50" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="I865" s="1" t="s">
         <v>656</v>
@@ -28588,7 +28604,7 @@
       <c r="G867" s="28"/>
       <c r="H867" s="53"/>
       <c r="I867" s="65" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="868" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -28607,7 +28623,7 @@
       <c r="G868" s="2"/>
       <c r="H868" s="50"/>
       <c r="I868" s="1" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="869" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28630,7 +28646,7 @@
       <c r="G869" s="29"/>
       <c r="H869" s="50"/>
       <c r="I869" s="1" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="870" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28653,7 +28669,7 @@
       <c r="G870" s="29"/>
       <c r="H870" s="50"/>
       <c r="I870" s="1" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="871" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28676,7 +28692,7 @@
       <c r="G871" s="29"/>
       <c r="H871" s="50"/>
       <c r="I871" s="1" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="872" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28698,7 +28714,7 @@
       </c>
       <c r="G872" s="8"/>
       <c r="H872" s="50" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="I872" s="1" t="s">
         <v>656</v>
@@ -28737,7 +28753,7 @@
       <c r="G874" s="28"/>
       <c r="H874" s="53"/>
       <c r="I874" s="65" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="875" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -28760,7 +28776,7 @@
       <c r="G875" s="29"/>
       <c r="H875" s="50"/>
       <c r="I875" s="1" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="876" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28783,7 +28799,7 @@
       <c r="G876" s="29"/>
       <c r="H876" s="50"/>
       <c r="I876" s="1" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="877" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28806,7 +28822,7 @@
       <c r="G877" s="29"/>
       <c r="H877" s="50"/>
       <c r="I877" s="1" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="878" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -28829,7 +28845,7 @@
       <c r="G878" s="29"/>
       <c r="H878" s="50"/>
       <c r="I878" s="1" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="879" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28848,7 +28864,7 @@
       <c r="G879" s="29"/>
       <c r="H879" s="50"/>
       <c r="I879" s="1" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="880" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28870,7 +28886,7 @@
       </c>
       <c r="G880" s="19"/>
       <c r="H880" s="50" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="I880" s="1" t="s">
         <v>656</v>
@@ -28895,7 +28911,7 @@
       </c>
       <c r="G881" s="8"/>
       <c r="H881" s="50" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="I881" s="1" t="s">
         <v>656</v>
@@ -28934,7 +28950,7 @@
       <c r="G883" s="28"/>
       <c r="H883" s="50"/>
       <c r="I883" s="65" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="884" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -28957,7 +28973,7 @@
       <c r="G884" s="29"/>
       <c r="H884" s="50"/>
       <c r="I884" s="1" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="885" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -28973,7 +28989,7 @@
       <c r="F885" s="2"/>
       <c r="G885" s="29"/>
       <c r="H885" s="50" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="I885" s="1" t="s">
         <v>656</v>
@@ -28999,7 +29015,7 @@
       <c r="G886" s="29"/>
       <c r="H886" s="50"/>
       <c r="I886" s="1" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="887" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29021,7 +29037,7 @@
       </c>
       <c r="G887" s="8"/>
       <c r="H887" s="50" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
       <c r="I887" s="1" t="s">
         <v>656</v>
@@ -29060,7 +29076,7 @@
       <c r="G889" s="28"/>
       <c r="H889" s="50"/>
       <c r="I889" s="51" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="890" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -29083,7 +29099,7 @@
       <c r="G890" s="29"/>
       <c r="H890" s="50"/>
       <c r="I890" s="1" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="891" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29099,7 +29115,7 @@
       <c r="F891" s="2"/>
       <c r="G891" s="29"/>
       <c r="H891" s="50" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="I891" s="1" t="s">
         <v>656</v>
@@ -29125,7 +29141,7 @@
       <c r="G892" s="29"/>
       <c r="H892" s="50"/>
       <c r="I892" s="1" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="893" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29147,7 +29163,7 @@
       </c>
       <c r="G893" s="8"/>
       <c r="H893" s="50" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
       <c r="I893" s="1" t="s">
         <v>656</v>
@@ -29186,7 +29202,7 @@
       <c r="G895" s="28"/>
       <c r="H895" s="50"/>
       <c r="I895" s="65" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="896" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -29205,7 +29221,7 @@
       <c r="G896" s="2"/>
       <c r="H896" s="50"/>
       <c r="I896" s="1" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="897" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29224,7 +29240,7 @@
       <c r="G897" s="2"/>
       <c r="H897" s="50"/>
       <c r="I897" s="1" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="898" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -29247,7 +29263,7 @@
       <c r="G898" s="29"/>
       <c r="H898" s="50"/>
       <c r="I898" s="1" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="899" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -29270,7 +29286,7 @@
       <c r="G899" s="29"/>
       <c r="H899" s="50"/>
       <c r="I899" s="1" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="900" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -29293,7 +29309,7 @@
       <c r="G900" s="29"/>
       <c r="H900" s="50"/>
       <c r="I900" s="1" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="901" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -29316,7 +29332,7 @@
       <c r="G901" s="29"/>
       <c r="H901" s="50"/>
       <c r="I901" s="1" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="902" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29332,7 +29348,7 @@
       <c r="F902" s="2"/>
       <c r="G902" s="29"/>
       <c r="H902" s="50" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="I902" s="1" t="s">
         <v>656</v>
@@ -29358,7 +29374,7 @@
       <c r="G903" s="29"/>
       <c r="H903" s="50"/>
       <c r="I903" s="1" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="904" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29374,7 +29390,7 @@
       <c r="F904" s="2"/>
       <c r="G904" s="29"/>
       <c r="H904" s="50" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="I904" s="1" t="s">
         <v>656</v>
@@ -29400,7 +29416,7 @@
       <c r="G905" s="29"/>
       <c r="H905" s="50"/>
       <c r="I905" s="1" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="906" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29422,7 +29438,7 @@
       </c>
       <c r="G906" s="8"/>
       <c r="H906" s="50" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="I906" s="1" t="s">
         <v>656</v>
@@ -29461,7 +29477,7 @@
       <c r="G908" s="28"/>
       <c r="H908" s="50"/>
       <c r="I908" s="58" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="909" spans="1:9" customFormat="1" ht="156" x14ac:dyDescent="0.3">
@@ -29480,7 +29496,7 @@
       <c r="G909" s="2"/>
       <c r="H909" s="50"/>
       <c r="I909" s="64" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="910" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -29503,7 +29519,7 @@
       <c r="G910" s="29"/>
       <c r="H910" s="50"/>
       <c r="I910" s="1" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="911" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -29526,7 +29542,7 @@
       <c r="G911" s="29"/>
       <c r="H911" s="50"/>
       <c r="I911" s="1" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="912" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29542,7 +29558,7 @@
       <c r="F912" s="2"/>
       <c r="G912" s="29"/>
       <c r="H912" s="50" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="I912" s="1" t="s">
         <v>656</v>
@@ -29568,7 +29584,7 @@
       <c r="G913" s="29"/>
       <c r="H913" s="50"/>
       <c r="I913" s="1" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="914" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29584,7 +29600,7 @@
       <c r="F914" s="2"/>
       <c r="G914" s="29"/>
       <c r="H914" s="50" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="I914" s="1" t="s">
         <v>656</v>
@@ -29610,7 +29626,7 @@
       <c r="G915" s="29"/>
       <c r="H915" s="50"/>
       <c r="I915" s="1" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="916" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29632,7 +29648,7 @@
       </c>
       <c r="G916" s="19"/>
       <c r="H916" s="50" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="I916" s="1" t="s">
         <v>656</v>
@@ -29657,7 +29673,7 @@
       </c>
       <c r="G917" s="8"/>
       <c r="H917" s="50" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="I917" s="1" t="s">
         <v>656</v>
@@ -29696,7 +29712,7 @@
       <c r="G919" s="28"/>
       <c r="H919" s="50"/>
       <c r="I919" s="65" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="920" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -29719,7 +29735,7 @@
       <c r="G920" s="29"/>
       <c r="H920" s="50"/>
       <c r="I920" s="1" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="921" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -29742,7 +29758,7 @@
       <c r="G921" s="29"/>
       <c r="H921" s="50"/>
       <c r="I921" s="1" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="922" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -29761,7 +29777,7 @@
       <c r="G922" s="29"/>
       <c r="H922" s="50"/>
       <c r="I922" s="1" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="923" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29783,7 +29799,7 @@
       </c>
       <c r="G923" s="8"/>
       <c r="H923" s="50" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="I923" s="1" t="s">
         <v>656</v>
@@ -29822,7 +29838,7 @@
       <c r="G925" s="28"/>
       <c r="H925" s="50"/>
       <c r="I925" s="65" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="926" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -29845,7 +29861,7 @@
       <c r="G926" s="29"/>
       <c r="H926" s="50"/>
       <c r="I926" s="1" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="927" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29861,7 +29877,7 @@
       <c r="F927" s="2"/>
       <c r="G927" s="29"/>
       <c r="H927" s="50" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="I927" s="1" t="s">
         <v>656</v>
@@ -29887,7 +29903,7 @@
       <c r="G928" s="29"/>
       <c r="H928" s="50"/>
       <c r="I928" s="1" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="929" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29903,7 +29919,7 @@
       <c r="F929" s="2"/>
       <c r="G929" s="29"/>
       <c r="H929" s="50" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="I929" s="1" t="s">
         <v>656</v>
@@ -29929,7 +29945,7 @@
       <c r="G930" s="29"/>
       <c r="H930" s="50"/>
       <c r="I930" s="1" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="931" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29945,7 +29961,7 @@
       <c r="F931" s="2"/>
       <c r="G931" s="29"/>
       <c r="H931" s="50" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="I931" s="1" t="s">
         <v>656</v>
@@ -29971,7 +29987,7 @@
       <c r="G932" s="29"/>
       <c r="H932" s="50"/>
       <c r="I932" s="1" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="933" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -29987,7 +30003,7 @@
       <c r="F933" s="2"/>
       <c r="G933" s="29"/>
       <c r="H933" s="50" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="I933" s="1" t="s">
         <v>656</v>
@@ -30013,7 +30029,7 @@
       <c r="G934" s="29"/>
       <c r="H934" s="48"/>
       <c r="I934" s="1" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="935" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30029,7 +30045,7 @@
       <c r="F935" s="2"/>
       <c r="G935" s="29"/>
       <c r="H935" s="48" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="I935" s="1" t="s">
         <v>656</v>
@@ -30055,7 +30071,7 @@
       <c r="G936" s="29"/>
       <c r="H936" s="50"/>
       <c r="I936" s="1" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="937" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30077,7 +30093,7 @@
       </c>
       <c r="G937" s="8"/>
       <c r="H937" s="50" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="I937" s="1" t="s">
         <v>656</v>
@@ -30116,7 +30132,7 @@
       <c r="G939" s="28"/>
       <c r="H939" s="50"/>
       <c r="I939" s="65" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="940" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -30139,7 +30155,7 @@
       <c r="G940" s="29"/>
       <c r="H940" s="50"/>
       <c r="I940" s="1" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="941" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -30162,7 +30178,7 @@
       <c r="G941" s="29"/>
       <c r="H941" s="50"/>
       <c r="I941" s="1" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="942" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30185,7 +30201,7 @@
       <c r="G942" s="29"/>
       <c r="H942" s="50"/>
       <c r="I942" s="1" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="943" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30208,7 +30224,7 @@
       <c r="G943" s="29"/>
       <c r="H943" s="50"/>
       <c r="I943" s="1" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="944" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30231,7 +30247,7 @@
       <c r="G944" s="29"/>
       <c r="H944" s="50"/>
       <c r="I944" s="1" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="945" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -30254,7 +30270,7 @@
       <c r="G945" s="29"/>
       <c r="H945" s="50"/>
       <c r="I945" s="1" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="946" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30270,7 +30286,7 @@
       <c r="F946" s="2"/>
       <c r="G946" s="29"/>
       <c r="H946" s="50" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="I946" s="1" t="s">
         <v>656</v>
@@ -30296,7 +30312,7 @@
       <c r="G947" s="29"/>
       <c r="H947" s="50"/>
       <c r="I947" s="1" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="948" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30312,7 +30328,7 @@
       <c r="F948" s="2"/>
       <c r="G948" s="29"/>
       <c r="H948" s="50" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="I948" s="1" t="s">
         <v>656</v>
@@ -30338,7 +30354,7 @@
       <c r="G949" s="29"/>
       <c r="H949" s="50"/>
       <c r="I949" s="1" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="950" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30354,7 +30370,7 @@
       <c r="F950" s="2"/>
       <c r="G950" s="29"/>
       <c r="H950" s="50" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="I950" s="1" t="s">
         <v>656</v>
@@ -30380,7 +30396,7 @@
       <c r="G951" s="29"/>
       <c r="H951" s="50"/>
       <c r="I951" s="1" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="952" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30396,7 +30412,7 @@
       <c r="F952" s="2"/>
       <c r="G952" s="29"/>
       <c r="H952" s="50" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="I952" s="1" t="s">
         <v>656</v>
@@ -30422,7 +30438,7 @@
       <c r="G953" s="29"/>
       <c r="H953" s="50"/>
       <c r="I953" s="1" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="954" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30438,7 +30454,7 @@
       <c r="F954" s="2"/>
       <c r="G954" s="29"/>
       <c r="H954" s="50" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="I954" s="1" t="s">
         <v>656</v>
@@ -30464,7 +30480,7 @@
       <c r="G955" s="29"/>
       <c r="H955" s="50"/>
       <c r="I955" s="1" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="956" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30486,7 +30502,7 @@
       </c>
       <c r="G956" s="8"/>
       <c r="H956" s="50" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="I956" s="1" t="s">
         <v>656</v>
@@ -30525,7 +30541,7 @@
       <c r="G958" s="28"/>
       <c r="H958" s="50"/>
       <c r="I958" s="65" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="959" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -30544,7 +30560,7 @@
       <c r="G959" s="2"/>
       <c r="H959" s="50"/>
       <c r="I959" s="1" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="960" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -30563,7 +30579,7 @@
       <c r="G960" s="29"/>
       <c r="H960" s="50"/>
       <c r="I960" s="1" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="961" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30582,7 +30598,7 @@
       <c r="G961" s="29"/>
       <c r="H961" s="50"/>
       <c r="I961" s="1" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="962" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -30605,7 +30621,7 @@
       <c r="G962" s="29"/>
       <c r="H962" s="50"/>
       <c r="I962" s="1" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="963" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30628,7 +30644,7 @@
       <c r="G963" s="29"/>
       <c r="H963" s="50"/>
       <c r="I963" s="1" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="964" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30644,7 +30660,7 @@
       <c r="F964" s="2"/>
       <c r="G964" s="29"/>
       <c r="H964" s="50" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="I964" s="1" t="s">
         <v>656</v>
@@ -30670,7 +30686,7 @@
       <c r="G965" s="29"/>
       <c r="H965" s="50"/>
       <c r="I965" s="1" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="966" spans="1:9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -30693,7 +30709,7 @@
       <c r="G966" s="29"/>
       <c r="H966" s="50"/>
       <c r="I966" s="65" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="967" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30709,7 +30725,7 @@
       <c r="F967" s="2"/>
       <c r="G967" s="29"/>
       <c r="H967" s="50" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="I967" s="1" t="s">
         <v>656</v>
@@ -30735,7 +30751,7 @@
       <c r="G968" s="29"/>
       <c r="H968" s="50"/>
       <c r="I968" s="1" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="969" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30751,7 +30767,7 @@
       <c r="F969" s="2"/>
       <c r="G969" s="29"/>
       <c r="H969" s="50" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="I969" s="1" t="s">
         <v>656</v>
@@ -30777,7 +30793,7 @@
       <c r="G970" s="29"/>
       <c r="H970" s="50"/>
       <c r="I970" s="1" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="971" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30793,7 +30809,7 @@
       <c r="F971" s="2"/>
       <c r="G971" s="29"/>
       <c r="H971" s="50" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="I971" s="1" t="s">
         <v>656</v>
@@ -30819,7 +30835,7 @@
       <c r="G972" s="29"/>
       <c r="H972" s="50"/>
       <c r="I972" s="1" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="973" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -30842,7 +30858,7 @@
       <c r="G973" s="29"/>
       <c r="H973" s="50"/>
       <c r="I973" s="1" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="974" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30864,7 +30880,7 @@
       </c>
       <c r="G974" s="19"/>
       <c r="H974" s="50" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="I974" s="1" t="s">
         <v>656</v>
@@ -30889,7 +30905,7 @@
       </c>
       <c r="G975" s="8"/>
       <c r="H975" s="50" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="I975" s="1" t="s">
         <v>656</v>
@@ -30928,7 +30944,7 @@
       <c r="G977" s="28"/>
       <c r="H977" s="50"/>
       <c r="I977" s="65" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="978" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -30951,7 +30967,7 @@
       <c r="G978" s="29"/>
       <c r="H978" s="50"/>
       <c r="I978" s="1" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="979" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -30967,7 +30983,7 @@
       <c r="F979" s="2"/>
       <c r="G979" s="29"/>
       <c r="H979" s="50" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="I979" s="1" t="s">
         <v>656</v>
@@ -30993,7 +31009,7 @@
       <c r="G980" s="29"/>
       <c r="H980" s="50"/>
       <c r="I980" s="1" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="981" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -31016,7 +31032,7 @@
       <c r="G981" s="29"/>
       <c r="H981" s="50"/>
       <c r="I981" s="1" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="982" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -31039,7 +31055,7 @@
       <c r="G982" s="29"/>
       <c r="H982" s="50"/>
       <c r="I982" s="1" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="983" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31061,7 +31077,7 @@
       </c>
       <c r="G983" s="8"/>
       <c r="H983" s="50" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="I983" s="1" t="s">
         <v>656</v>
@@ -31100,7 +31116,7 @@
       <c r="G985" s="28"/>
       <c r="H985" s="50"/>
       <c r="I985" s="65" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="986" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -31119,7 +31135,7 @@
       <c r="G986" s="2"/>
       <c r="H986" s="50"/>
       <c r="I986" s="1" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="987" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -31142,7 +31158,7 @@
       <c r="G987" s="29"/>
       <c r="H987" s="50"/>
       <c r="I987" s="1" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="988" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31165,7 +31181,7 @@
       <c r="G988" s="29"/>
       <c r="H988" s="50"/>
       <c r="I988" s="1" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="989" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31181,7 +31197,7 @@
       <c r="F989" s="2"/>
       <c r="G989" s="29"/>
       <c r="H989" s="50" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="I989" s="1" t="s">
         <v>656</v>
@@ -31207,7 +31223,7 @@
       <c r="G990" s="29"/>
       <c r="H990" s="50"/>
       <c r="I990" s="1" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="991" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31223,7 +31239,7 @@
       <c r="F991" s="2"/>
       <c r="G991" s="29"/>
       <c r="H991" s="50" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="I991" s="1" t="s">
         <v>656</v>
@@ -31249,7 +31265,7 @@
       <c r="G992" s="29"/>
       <c r="H992" s="50"/>
       <c r="I992" s="1" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="993" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31271,7 +31287,7 @@
       </c>
       <c r="G993" s="8"/>
       <c r="H993" s="50" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="I993" s="1" t="s">
         <v>656</v>
@@ -31310,7 +31326,7 @@
       <c r="G995" s="28"/>
       <c r="H995" s="50"/>
       <c r="I995" s="65" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="996" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -31333,7 +31349,7 @@
       <c r="G996" s="29"/>
       <c r="H996" s="50"/>
       <c r="I996" s="1" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="997" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -31356,7 +31372,7 @@
       <c r="G997" s="29"/>
       <c r="H997" s="50"/>
       <c r="I997" s="1" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="998" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31378,7 +31394,7 @@
       </c>
       <c r="G998" s="8"/>
       <c r="H998" s="50" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="I998" s="1" t="s">
         <v>656</v>
@@ -31416,7 +31432,9 @@
       <c r="F1000" s="2"/>
       <c r="G1000" s="28"/>
       <c r="H1000" s="50"/>
-      <c r="I1000" s="1"/>
+      <c r="I1000" s="84" t="s">
+        <v>2974</v>
+      </c>
     </row>
     <row r="1001" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1001" s="10"/>
@@ -31434,7 +31452,7 @@
       <c r="G1001" s="29"/>
       <c r="H1001" s="50"/>
       <c r="I1001" s="1" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="1002" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -31457,7 +31475,7 @@
       <c r="G1002" s="29"/>
       <c r="H1002" s="50"/>
       <c r="I1002" s="1" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="1003" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -31480,7 +31498,7 @@
       <c r="G1003" s="29"/>
       <c r="H1003" s="50"/>
       <c r="I1003" s="1" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="1004" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -31503,7 +31521,7 @@
       <c r="G1004" s="29"/>
       <c r="H1004" s="50"/>
       <c r="I1004" s="1" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="1005" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31526,7 +31544,7 @@
       <c r="G1005" s="29"/>
       <c r="H1005" s="50"/>
       <c r="I1005" s="1" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="1006" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31548,7 +31566,7 @@
       </c>
       <c r="G1006" s="8"/>
       <c r="H1006" s="50" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="I1006" s="1" t="s">
         <v>656</v>
@@ -31567,7 +31585,7 @@
       <c r="F1007" s="2"/>
       <c r="G1007" s="28"/>
       <c r="H1007" s="50" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1007" s="1" t="s">
         <v>656</v>
@@ -31587,7 +31605,7 @@
       <c r="G1008" s="28"/>
       <c r="H1008" s="50"/>
       <c r="I1008" s="65" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="1009" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -31606,7 +31624,7 @@
       <c r="G1009" s="29"/>
       <c r="H1009" s="50"/>
       <c r="I1009" s="1" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="1010" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -31629,7 +31647,7 @@
       <c r="G1010" s="29"/>
       <c r="H1010" s="1"/>
       <c r="I1010" s="1" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="1011" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -31648,7 +31666,7 @@
       <c r="G1011" s="29"/>
       <c r="H1011" s="1"/>
       <c r="I1011" s="1" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="1012" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31664,7 +31682,7 @@
       <c r="F1012" s="2"/>
       <c r="G1012" s="29"/>
       <c r="H1012" s="1" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="I1012" s="1" t="s">
         <v>656</v>
@@ -31690,7 +31708,7 @@
       <c r="G1013" s="29"/>
       <c r="H1013" s="1"/>
       <c r="I1013" s="1" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="1014" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31706,7 +31724,7 @@
       <c r="F1014" s="2"/>
       <c r="G1014" s="29"/>
       <c r="H1014" s="1" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="I1014" s="1" t="s">
         <v>656</v>
@@ -31732,7 +31750,7 @@
       <c r="G1015" s="29"/>
       <c r="H1015" s="1"/>
       <c r="I1015" s="1" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="1016" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31752,7 +31770,7 @@
       </c>
       <c r="G1016" s="19"/>
       <c r="H1016" s="1" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="I1016" s="1" t="s">
         <v>656</v>
@@ -31775,7 +31793,7 @@
       </c>
       <c r="G1017" s="8"/>
       <c r="H1017" s="1" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="I1017" s="1" t="s">
         <v>656</v>
@@ -31794,7 +31812,7 @@
       <c r="F1018" s="2"/>
       <c r="G1018" s="28"/>
       <c r="H1018" s="50" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1018" s="1" t="s">
         <v>656</v>
@@ -31814,7 +31832,7 @@
       <c r="G1019" s="28"/>
       <c r="H1019" s="48"/>
       <c r="I1019" s="58" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1020" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -31837,7 +31855,7 @@
       <c r="G1020" s="29"/>
       <c r="H1020" s="48"/>
       <c r="I1020" s="1" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="1021" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31853,7 +31871,7 @@
       <c r="F1021" s="2"/>
       <c r="G1021" s="29"/>
       <c r="H1021" s="48" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="I1021" s="1" t="s">
         <v>656</v>
@@ -31879,7 +31897,7 @@
       <c r="G1022" s="29"/>
       <c r="H1022" s="48"/>
       <c r="I1022" s="1" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="1023" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31895,7 +31913,7 @@
       <c r="F1023" s="2"/>
       <c r="G1023" s="29"/>
       <c r="H1023" s="48" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="I1023" s="1" t="s">
         <v>656</v>
@@ -31921,7 +31939,7 @@
       <c r="G1024" s="29"/>
       <c r="H1024" s="48"/>
       <c r="I1024" s="1" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="1025" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31937,7 +31955,7 @@
       <c r="F1025" s="2"/>
       <c r="G1025" s="29"/>
       <c r="H1025" s="48" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="I1025" s="1" t="s">
         <v>656</v>
@@ -31963,7 +31981,7 @@
       <c r="G1026" s="29"/>
       <c r="H1026" s="48"/>
       <c r="I1026" s="48" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="1027" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -31979,7 +31997,7 @@
       <c r="F1027" s="2"/>
       <c r="G1027" s="29"/>
       <c r="H1027" s="48" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="I1027" s="1" t="s">
         <v>656</v>
@@ -32005,7 +32023,7 @@
       <c r="G1028" s="29"/>
       <c r="H1028" s="48"/>
       <c r="I1028" s="1" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="1029" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32021,7 +32039,7 @@
       <c r="F1029" s="2"/>
       <c r="G1029" s="29"/>
       <c r="H1029" s="48" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="I1029" s="1" t="s">
         <v>656</v>
@@ -32047,7 +32065,7 @@
       <c r="G1030" s="29"/>
       <c r="H1030" s="48"/>
       <c r="I1030" s="1" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1031" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32069,7 +32087,7 @@
       </c>
       <c r="G1031" s="8"/>
       <c r="H1031" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="I1031" s="1" t="s">
         <v>656</v>
@@ -32088,7 +32106,7 @@
       <c r="F1032" s="2"/>
       <c r="G1032" s="28"/>
       <c r="H1032" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1032" s="1" t="s">
         <v>656</v>
@@ -32108,7 +32126,7 @@
       <c r="G1033" s="28"/>
       <c r="H1033" s="48"/>
       <c r="I1033" s="58" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1034" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -32127,7 +32145,7 @@
       <c r="G1034" s="29"/>
       <c r="H1034" s="48"/>
       <c r="I1034" s="1" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1035" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32150,7 +32168,7 @@
       <c r="G1035" s="29"/>
       <c r="H1035" s="48"/>
       <c r="I1035" s="1" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="1036" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32173,7 +32191,7 @@
       <c r="G1036" s="29"/>
       <c r="H1036" s="48"/>
       <c r="I1036" s="1" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="1037" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32196,7 +32214,7 @@
       <c r="G1037" s="29"/>
       <c r="H1037" s="48"/>
       <c r="I1037" s="1" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="1038" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32212,7 +32230,7 @@
       <c r="F1038" s="2"/>
       <c r="G1038" s="29"/>
       <c r="H1038" s="48" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="I1038" s="1" t="s">
         <v>656</v>
@@ -32238,7 +32256,7 @@
       <c r="G1039" s="29"/>
       <c r="H1039" s="48"/>
       <c r="I1039" s="1" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="1040" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32254,7 +32272,7 @@
       <c r="F1040" s="2"/>
       <c r="G1040" s="29"/>
       <c r="H1040" s="48" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="I1040" s="1" t="s">
         <v>656</v>
@@ -32280,7 +32298,7 @@
       <c r="G1041" s="29"/>
       <c r="H1041" s="48"/>
       <c r="I1041" s="1" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="1042" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32302,7 +32320,7 @@
       </c>
       <c r="G1042" s="19"/>
       <c r="H1042" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="I1042" s="1" t="s">
         <v>656</v>
@@ -32327,7 +32345,7 @@
       </c>
       <c r="G1043" s="8"/>
       <c r="H1043" s="48" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="I1043" s="1" t="s">
         <v>656</v>
@@ -32346,7 +32364,7 @@
       <c r="F1044" s="2"/>
       <c r="G1044" s="28"/>
       <c r="H1044" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1044" s="1" t="s">
         <v>656</v>
@@ -32366,7 +32384,7 @@
       <c r="G1045" s="28"/>
       <c r="H1045" s="48"/>
       <c r="I1045" s="49" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="1046" spans="1:9" customFormat="1" ht="109.2" x14ac:dyDescent="0.3">
@@ -32389,7 +32407,7 @@
       <c r="G1046" s="29"/>
       <c r="H1046" s="48"/>
       <c r="I1046" s="1" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="1047" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32411,7 +32429,7 @@
       </c>
       <c r="G1047" s="8"/>
       <c r="H1047" s="48" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="I1047" s="1" t="s">
         <v>656</v>
@@ -32430,7 +32448,7 @@
       <c r="F1048" s="2"/>
       <c r="G1048" s="28"/>
       <c r="H1048" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1048" s="1" t="s">
         <v>656</v>
@@ -32450,7 +32468,7 @@
       <c r="G1049" s="28"/>
       <c r="H1049" s="48"/>
       <c r="I1049" s="58" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="1050" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -32473,7 +32491,7 @@
       <c r="G1050" s="29"/>
       <c r="H1050" s="48"/>
       <c r="I1050" s="1" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="1051" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -32496,7 +32514,7 @@
       <c r="G1051" s="29"/>
       <c r="H1051" s="48"/>
       <c r="I1051" s="1" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="1052" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -32519,7 +32537,7 @@
       <c r="G1052" s="29"/>
       <c r="H1052" s="48"/>
       <c r="I1052" s="1" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="1053" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -32542,7 +32560,7 @@
       <c r="G1053" s="29"/>
       <c r="H1053" s="48"/>
       <c r="I1053" s="1" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="1054" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -32565,7 +32583,7 @@
       <c r="G1054" s="29"/>
       <c r="H1054" s="48"/>
       <c r="I1054" s="1" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="1055" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32587,7 +32605,7 @@
       </c>
       <c r="G1055" s="8"/>
       <c r="H1055" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="I1055" s="1" t="s">
         <v>656</v>
@@ -32606,7 +32624,7 @@
       <c r="F1056" s="2"/>
       <c r="G1056" s="28"/>
       <c r="H1056" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1056" s="1" t="s">
         <v>656</v>
@@ -32626,7 +32644,7 @@
       <c r="G1057" s="28"/>
       <c r="H1057" s="48"/>
       <c r="I1057" s="58" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="1058" spans="1:9" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
@@ -32649,7 +32667,7 @@
       <c r="G1058" s="29"/>
       <c r="H1058" s="48"/>
       <c r="I1058" s="1" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="1059" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32665,7 +32683,7 @@
       <c r="F1059" s="2"/>
       <c r="G1059" s="29"/>
       <c r="H1059" s="48" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="I1059" s="1" t="s">
         <v>656</v>
@@ -32691,7 +32709,7 @@
       <c r="G1060" s="29"/>
       <c r="H1060" s="48"/>
       <c r="I1060" s="1" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="1061" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32707,7 +32725,7 @@
       <c r="F1061" s="2"/>
       <c r="G1061" s="29"/>
       <c r="H1061" s="48" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="I1061" s="1" t="s">
         <v>656</v>
@@ -32733,7 +32751,7 @@
       <c r="G1062" s="29"/>
       <c r="H1062" s="48"/>
       <c r="I1062" s="1" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="1063" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32749,7 +32767,7 @@
       <c r="F1063" s="2"/>
       <c r="G1063" s="29"/>
       <c r="H1063" s="48" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="I1063" s="1" t="s">
         <v>656</v>
@@ -32775,7 +32793,7 @@
       <c r="G1064" s="29"/>
       <c r="H1064" s="48"/>
       <c r="I1064" s="1" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="1065" spans="1:9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -32791,7 +32809,7 @@
       <c r="F1065" s="2"/>
       <c r="G1065" s="29"/>
       <c r="H1065" s="48" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="I1065" s="1" t="s">
         <v>656</v>
@@ -32817,7 +32835,7 @@
       <c r="G1066" s="29"/>
       <c r="H1066" s="48"/>
       <c r="I1066" s="1" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="1067" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32833,7 +32851,7 @@
       <c r="F1067" s="2"/>
       <c r="G1067" s="29"/>
       <c r="H1067" s="48" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="I1067" s="1" t="s">
         <v>656</v>
@@ -32859,7 +32877,7 @@
       <c r="G1068" s="29"/>
       <c r="H1068" s="48"/>
       <c r="I1068" s="1" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="1069" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32881,7 +32899,7 @@
       </c>
       <c r="G1069" s="8"/>
       <c r="H1069" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="I1069" s="1" t="s">
         <v>656</v>
@@ -32900,7 +32918,7 @@
       <c r="F1070" s="2"/>
       <c r="G1070" s="28"/>
       <c r="H1070" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1070" s="1" t="s">
         <v>656</v>
@@ -32920,7 +32938,7 @@
       <c r="G1071" s="28"/>
       <c r="H1071" s="48"/>
       <c r="I1071" s="58" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="1072" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -32939,7 +32957,7 @@
       <c r="G1072" s="2"/>
       <c r="H1072" s="48"/>
       <c r="I1072" s="1" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="1073" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -32964,7 +32982,7 @@
       </c>
       <c r="H1073" s="48"/>
       <c r="I1073" s="1" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="1074" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -32989,7 +33007,7 @@
       </c>
       <c r="H1074" s="48"/>
       <c r="I1074" s="1" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="1075" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -33014,7 +33032,7 @@
       </c>
       <c r="H1075" s="48"/>
       <c r="I1075" s="1" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="1076" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -33039,7 +33057,7 @@
       </c>
       <c r="H1076" s="48"/>
       <c r="I1076" s="1" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="1077" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33055,7 +33073,7 @@
       <c r="F1077" s="2"/>
       <c r="G1077" s="29"/>
       <c r="H1077" s="48" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="I1077" s="1" t="s">
         <v>656</v>
@@ -33081,7 +33099,7 @@
       <c r="G1078" s="29"/>
       <c r="H1078" s="48"/>
       <c r="I1078" s="1" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="1079" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33104,7 +33122,7 @@
       <c r="G1079" s="29"/>
       <c r="H1079" s="48"/>
       <c r="I1079" s="1" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="1080" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33126,7 +33144,7 @@
       </c>
       <c r="G1080" s="8"/>
       <c r="H1080" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="I1080" s="1" t="s">
         <v>656</v>
@@ -33145,7 +33163,7 @@
       <c r="F1081" s="2"/>
       <c r="G1081" s="28"/>
       <c r="H1081" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1081" s="1" t="s">
         <v>656</v>
@@ -33165,7 +33183,7 @@
       <c r="G1082" s="28"/>
       <c r="H1082" s="48"/>
       <c r="I1082" s="58" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="1083" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -33188,7 +33206,7 @@
       <c r="G1083" s="29"/>
       <c r="H1083" s="48"/>
       <c r="I1083" s="1" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="1084" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -33207,7 +33225,7 @@
       <c r="G1084" s="2"/>
       <c r="H1084" s="48"/>
       <c r="I1084" s="1" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="1085" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33229,7 +33247,7 @@
       </c>
       <c r="G1085" s="8"/>
       <c r="H1085" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="I1085" s="1" t="s">
         <v>656</v>
@@ -33248,7 +33266,7 @@
       <c r="F1086" s="2"/>
       <c r="G1086" s="28"/>
       <c r="H1086" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1086" s="1" t="s">
         <v>656</v>
@@ -33268,7 +33286,7 @@
       <c r="G1087" s="28"/>
       <c r="H1087" s="48"/>
       <c r="I1087" s="58" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="1088" spans="1:9" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
@@ -33291,7 +33309,7 @@
       <c r="G1088" s="29"/>
       <c r="H1088" s="48"/>
       <c r="I1088" s="1" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="1089" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33314,7 +33332,7 @@
       <c r="G1089" s="29"/>
       <c r="H1089" s="48"/>
       <c r="I1089" s="1" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="1090" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33337,7 +33355,7 @@
       <c r="G1090" s="29"/>
       <c r="H1090" s="48"/>
       <c r="I1090" s="1" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="1091" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33360,7 +33378,7 @@
       <c r="G1091" s="29"/>
       <c r="H1091" s="48"/>
       <c r="I1091" s="1" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="1092" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33383,7 +33401,7 @@
       <c r="G1092" s="29"/>
       <c r="H1092" s="48"/>
       <c r="I1092" s="1" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="1093" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33406,7 +33424,7 @@
       <c r="G1093" s="29"/>
       <c r="H1093" s="48"/>
       <c r="I1093" s="1" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="1094" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33422,7 +33440,7 @@
       <c r="F1094" s="2"/>
       <c r="G1094" s="29"/>
       <c r="H1094" s="48" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="I1094" s="1" t="s">
         <v>656</v>
@@ -33448,7 +33466,7 @@
       <c r="G1095" s="29"/>
       <c r="H1095" s="48"/>
       <c r="I1095" s="1" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="1096" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33464,7 +33482,7 @@
       <c r="F1096" s="2"/>
       <c r="G1096" s="29"/>
       <c r="H1096" s="48" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="I1096" s="1" t="s">
         <v>656</v>
@@ -33490,7 +33508,7 @@
       <c r="G1097" s="29"/>
       <c r="H1097" s="48"/>
       <c r="I1097" s="1" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="1098" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33512,7 +33530,7 @@
       </c>
       <c r="G1098" s="19"/>
       <c r="H1098" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="I1098" s="1" t="s">
         <v>656</v>
@@ -33537,7 +33555,7 @@
       </c>
       <c r="G1099" s="8"/>
       <c r="H1099" s="48" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="I1099" s="1" t="s">
         <v>656</v>
@@ -33556,7 +33574,7 @@
       <c r="F1100" s="2"/>
       <c r="G1100" s="28"/>
       <c r="H1100" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1100" s="1" t="s">
         <v>656</v>
@@ -33576,7 +33594,7 @@
       <c r="G1101" s="28"/>
       <c r="H1101" s="48"/>
       <c r="I1101" s="58" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="1102" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33595,7 +33613,7 @@
       <c r="G1102" s="2"/>
       <c r="H1102" s="48"/>
       <c r="I1102" s="1" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="1103" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33618,7 +33636,7 @@
       <c r="G1103" s="29"/>
       <c r="H1103" s="48"/>
       <c r="I1103" s="1" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="1104" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33641,7 +33659,7 @@
       <c r="G1104" s="29"/>
       <c r="H1104" s="48"/>
       <c r="I1104" s="1" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="1105" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33660,7 +33678,7 @@
       <c r="G1105" s="29"/>
       <c r="H1105" s="48"/>
       <c r="I1105" s="1" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="1106" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33683,7 +33701,7 @@
       <c r="G1106" s="29"/>
       <c r="H1106" s="48"/>
       <c r="I1106" s="1" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="1107" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33706,7 +33724,7 @@
       <c r="G1107" s="29"/>
       <c r="H1107" s="48"/>
       <c r="I1107" s="1" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="1108" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33729,7 +33747,7 @@
       <c r="G1108" s="29"/>
       <c r="H1108" s="48"/>
       <c r="I1108" s="1" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1109" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33748,7 +33766,7 @@
       <c r="G1109" s="29"/>
       <c r="H1109" s="48"/>
       <c r="I1109" s="1" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="1110" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33771,7 +33789,7 @@
       <c r="G1110" s="29"/>
       <c r="H1110" s="48"/>
       <c r="I1110" s="1" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="1111" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33794,7 +33812,7 @@
       <c r="G1111" s="29"/>
       <c r="H1111" s="48"/>
       <c r="I1111" s="1" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="1112" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33816,7 +33834,7 @@
       </c>
       <c r="G1112" s="8"/>
       <c r="H1112" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="I1112" s="1" t="s">
         <v>656</v>
@@ -33835,7 +33853,7 @@
       <c r="F1113" s="2"/>
       <c r="G1113" s="28"/>
       <c r="H1113" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1113" s="1" t="s">
         <v>656</v>
@@ -33855,7 +33873,7 @@
       <c r="G1114" s="28"/>
       <c r="H1114" s="48"/>
       <c r="I1114" s="58" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="1115" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33874,7 +33892,7 @@
       <c r="G1115" s="2"/>
       <c r="H1115" s="48"/>
       <c r="I1115" s="1" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="1116" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -33897,7 +33915,7 @@
       <c r="G1116" s="29"/>
       <c r="H1116" s="48"/>
       <c r="I1116" s="1" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="1117" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33920,7 +33938,7 @@
       <c r="G1117" s="29"/>
       <c r="H1117" s="48"/>
       <c r="I1117" s="1" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="1118" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -33943,7 +33961,7 @@
       <c r="G1118" s="29"/>
       <c r="H1118" s="48"/>
       <c r="I1118" s="1" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="1119" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -33966,7 +33984,7 @@
       <c r="G1119" s="29"/>
       <c r="H1119" s="48"/>
       <c r="I1119" s="1" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="1120" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -33989,7 +34007,7 @@
       <c r="G1120" s="29"/>
       <c r="H1120" s="48"/>
       <c r="I1120" s="1" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="1121" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34012,7 +34030,7 @@
       <c r="G1121" s="29"/>
       <c r="H1121" s="48"/>
       <c r="I1121" s="1" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="1122" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34035,7 +34053,7 @@
       <c r="G1122" s="29"/>
       <c r="H1122" s="48"/>
       <c r="I1122" s="1" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
     </row>
     <row r="1123" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34051,7 +34069,7 @@
       <c r="F1123" s="2"/>
       <c r="G1123" s="29"/>
       <c r="H1123" s="48" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="I1123" s="1" t="s">
         <v>656</v>
@@ -34077,7 +34095,7 @@
       <c r="G1124" s="29"/>
       <c r="H1124" s="48"/>
       <c r="I1124" s="1" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="1125" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34100,7 +34118,7 @@
       <c r="G1125" s="29"/>
       <c r="H1125" s="48"/>
       <c r="I1125" s="1" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="1126" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34116,7 +34134,7 @@
       <c r="F1126" s="2"/>
       <c r="G1126" s="29"/>
       <c r="H1126" s="48" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="I1126" s="1" t="s">
         <v>656</v>
@@ -34142,7 +34160,7 @@
       <c r="G1127" s="29"/>
       <c r="H1127" s="48"/>
       <c r="I1127" s="1" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="1128" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -34165,7 +34183,7 @@
       <c r="G1128" s="29"/>
       <c r="H1128" s="48"/>
       <c r="I1128" s="1" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="1129" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -34188,7 +34206,7 @@
       <c r="G1129" s="29"/>
       <c r="H1129" s="48"/>
       <c r="I1129" s="1" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="1130" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34204,7 +34222,7 @@
       <c r="F1130" s="2"/>
       <c r="G1130" s="29"/>
       <c r="H1130" s="48" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="I1130" s="1" t="s">
         <v>656</v>
@@ -34230,7 +34248,7 @@
       <c r="G1131" s="29"/>
       <c r="H1131" s="48"/>
       <c r="I1131" s="1" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="1132" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34252,7 +34270,7 @@
       </c>
       <c r="G1132" s="8"/>
       <c r="H1132" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="I1132" s="1" t="s">
         <v>656</v>
@@ -34271,7 +34289,7 @@
       <c r="F1133" s="2"/>
       <c r="G1133" s="28"/>
       <c r="H1133" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1133" s="1" t="s">
         <v>656</v>
@@ -34291,7 +34309,7 @@
       <c r="G1134" s="28"/>
       <c r="H1134" s="48"/>
       <c r="I1134" s="58" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="1135" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34310,7 +34328,7 @@
       <c r="G1135" s="2"/>
       <c r="H1135" s="48"/>
       <c r="I1135" s="1" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="1136" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -34333,7 +34351,7 @@
       <c r="G1136" s="29"/>
       <c r="H1136" s="48"/>
       <c r="I1136" s="1" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="1137" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34356,7 +34374,7 @@
       <c r="G1137" s="29"/>
       <c r="H1137" s="48"/>
       <c r="I1137" s="1" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="1138" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34379,7 +34397,7 @@
       <c r="G1138" s="29"/>
       <c r="H1138" s="48"/>
       <c r="I1138" s="1" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="1139" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34402,7 +34420,7 @@
       <c r="G1139" s="29"/>
       <c r="H1139" s="48"/>
       <c r="I1139" s="1" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="1140" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34425,7 +34443,7 @@
       <c r="G1140" s="29"/>
       <c r="H1140" s="48"/>
       <c r="I1140" s="1" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="1141" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -34448,7 +34466,7 @@
       <c r="G1141" s="29"/>
       <c r="H1141" s="48"/>
       <c r="I1141" s="1" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="1142" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34471,7 +34489,7 @@
       <c r="G1142" s="29"/>
       <c r="H1142" s="48"/>
       <c r="I1142" s="1" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="1143" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34487,7 +34505,7 @@
       <c r="F1143" s="2"/>
       <c r="G1143" s="29"/>
       <c r="H1143" s="48" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="I1143" s="1" t="s">
         <v>656</v>
@@ -34513,7 +34531,7 @@
       <c r="G1144" s="29"/>
       <c r="H1144" s="48"/>
       <c r="I1144" s="1" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="1145" spans="1:9" customFormat="1" ht="78" x14ac:dyDescent="0.3">
@@ -34536,7 +34554,7 @@
       <c r="G1145" s="29"/>
       <c r="H1145" s="48"/>
       <c r="I1145" s="1" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="1146" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34557,7 +34575,7 @@
       <c r="G1146" s="29"/>
       <c r="H1146" s="48"/>
       <c r="I1146" s="1" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="1147" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34573,7 +34591,7 @@
       <c r="F1147" s="2"/>
       <c r="G1147" s="29"/>
       <c r="H1147" s="48" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="I1147" s="1" t="s">
         <v>656</v>
@@ -34599,7 +34617,7 @@
       <c r="G1148" s="29"/>
       <c r="H1148" s="48"/>
       <c r="I1148" s="1" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="1149" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34621,7 +34639,7 @@
       </c>
       <c r="G1149" s="8"/>
       <c r="H1149" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="I1149" s="1" t="s">
         <v>656</v>
@@ -34640,7 +34658,7 @@
       <c r="F1150" s="2"/>
       <c r="G1150" s="28"/>
       <c r="H1150" s="48" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="I1150" s="1" t="s">
         <v>656</v>
@@ -34660,7 +34678,7 @@
       <c r="G1151" s="28"/>
       <c r="H1151" s="48"/>
       <c r="I1151" s="58" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="1152" spans="1:9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
@@ -34679,7 +34697,7 @@
       <c r="G1152" s="2"/>
       <c r="H1152" s="48"/>
       <c r="I1152" s="1" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="1153" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34702,7 +34720,7 @@
       <c r="G1153" s="29"/>
       <c r="H1153" s="48"/>
       <c r="I1153" s="1" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="1154" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34725,7 +34743,7 @@
       <c r="G1154" s="29"/>
       <c r="H1154" s="48"/>
       <c r="I1154" s="1" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="1155" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34741,7 +34759,7 @@
       <c r="F1155" s="2"/>
       <c r="G1155" s="2"/>
       <c r="H1155" s="48" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="I1155" s="1" t="s">
         <v>656</v>
@@ -34767,7 +34785,7 @@
       <c r="G1156" s="2"/>
       <c r="H1156" s="48"/>
       <c r="I1156" s="1" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="1157" spans="1:9" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
@@ -34790,7 +34808,7 @@
       <c r="G1157" s="2"/>
       <c r="H1157" s="48"/>
       <c r="I1157" s="1" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="1158" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34806,7 +34824,7 @@
       <c r="F1158" s="2"/>
       <c r="G1158" s="2"/>
       <c r="H1158" s="48" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="I1158" s="1" t="s">
         <v>656</v>
@@ -34832,7 +34850,7 @@
       <c r="G1159" s="2"/>
       <c r="H1159" s="48"/>
       <c r="I1159" s="1" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="1160" spans="1:9" customFormat="1" x14ac:dyDescent="0.3">
@@ -34878,7 +34896,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
     </row>
   </sheetData>
@@ -34910,7 +34928,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="E1" s="76" t="s">
         <v>1914</v>
@@ -34927,10 +34945,10 @@
         <v>635</v>
       </c>
       <c r="D2" s="76" t="s">
+        <v>2953</v>
+      </c>
+      <c r="E2" s="76" t="s">
         <v>2954</v>
-      </c>
-      <c r="E2" s="76" t="s">
-        <v>2955</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="78" x14ac:dyDescent="0.3">
@@ -34944,10 +34962,10 @@
         <v>637</v>
       </c>
       <c r="D3" s="76" t="s">
+        <v>2955</v>
+      </c>
+      <c r="E3" s="76" t="s">
         <v>2956</v>
-      </c>
-      <c r="E3" s="76" t="s">
-        <v>2957</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="78" x14ac:dyDescent="0.3">
@@ -34961,10 +34979,10 @@
         <v>639</v>
       </c>
       <c r="D4" s="76" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="E4" s="76" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="93.6" x14ac:dyDescent="0.3">
@@ -34978,10 +34996,10 @@
         <v>641</v>
       </c>
       <c r="D5" s="76" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="E5" s="76" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="78" x14ac:dyDescent="0.3">
@@ -34995,10 +35013,10 @@
         <v>643</v>
       </c>
       <c r="D6" s="76" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="E6" s="76" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="78" x14ac:dyDescent="0.3">
@@ -35012,10 +35030,10 @@
         <v>645</v>
       </c>
       <c r="D7" s="76" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="E7" s="76" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -35029,10 +35047,10 @@
         <v>442</v>
       </c>
       <c r="D8" s="76" t="s">
+        <v>2961</v>
+      </c>
+      <c r="E8" s="78" t="s">
         <v>2962</v>
-      </c>
-      <c r="E8" s="78" t="s">
-        <v>2963</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -35046,10 +35064,10 @@
         <v>442</v>
       </c>
       <c r="D9" s="76" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="E9" s="78" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -35063,10 +35081,10 @@
         <v>442</v>
       </c>
       <c r="D10" s="76" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="E10" s="78" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -35080,10 +35098,10 @@
         <v>442</v>
       </c>
       <c r="D11" s="76" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="E11" s="78" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -35097,10 +35115,10 @@
         <v>442</v>
       </c>
       <c r="D12" s="76" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="E12" s="78" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
